--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-609.7700000000004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.49611e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-44.923</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>13.42923533289388</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.34699151663602</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.442x + -34949.740</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.322490181638291e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5583.107734286695</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.807594656385111</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-569.1500000000005</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.56976e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-46.047</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>12.12322668149448</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.52505523349632</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 7.622x + -34247.625</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.08515318850282e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5386.849633954452</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000017e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8077105756396228</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-509.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.59836e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-46.49</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>17.3900891632371</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.40987055692312</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 8.656x + -38595.477</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.216578086636515e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5304.605237462032</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000373e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8076135668339688</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-484.1499999999996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.6234e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-46.905</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>19.12621404997642</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.66349059289855</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.005x + -39672.828</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.524288877266776e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5230.242124471747</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.0000000000002e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8076913251510853</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-472.3000000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.65025e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-47.29</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>19.83439615422354</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.77103415637386</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.162x + -39709.587</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.028636438670053e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5142.944730989095</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000073e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8079238008466673</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-456.46</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.67483e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-47.697</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>21.2096147790489</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.92295397944612</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.393x + -40150.359</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.708709045667614e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5063.695151031015</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8081783252032975</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-466.8000000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.69992e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-48.097</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>15.25971321630329</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.53988841734612</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 8.832x + -36995.665</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.425339802973112e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4987.932255327967</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8084622940808742</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-461.8400000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.72076e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-48.47</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>15.5631887807812</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.59262009627565</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 8.905x + -36805.816</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.097209174254449e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4916.332228474741</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000002425e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8087638652576949</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-446.4000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.74308e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-48.819</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>16.00133738135376</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.71499740390355</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.080x + -37054.328</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>652.3999456314157</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7507.460051448403</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.729412589657326e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6863249578181161</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-428.7399999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.76688e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-49.235</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>16.82244251390729</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.8515428256655</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.283x + -37406.305</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.662142564047953e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4783.521996762501</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8094284217404251</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-525.6799999999994</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.62054e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-45.559</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>14.95531914893608</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.00084306418941</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.145x + -35638.011</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.041712370402108e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5190.418689250138</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8079321386866858</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-514.4899999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.68724e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-46.652</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>12.49007926782028</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.94208340623368</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.077x + -33841.967</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.282798808123782e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5007.551366894228</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000088e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8080815158669509</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-492.6700000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.71526e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-47.125</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>13.20275783029324</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.14986634109481</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 8.324x + -34389.509</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>664.577608704921</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7616.150121410304</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7.465314260754322e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.6878099349073267</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-460.7600000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.73552e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-47.463</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>18.27231510342859</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.74338985397785</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.121x + -37435.237</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.915408073978983e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4868.791522028605</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000915e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.808044207624542</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-469.7600000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.75917e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-47.875</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>13.82611633557498</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.48099414394134</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.751x + -35290.506</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.313112773867714e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4804.054973645768</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8081749170101792</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-462.7399999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.77969e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-48.212</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>14.13579026141829</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.58050226954892</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.888x + -35402.636</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.042814161225317e-18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4739.387227142071</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8084382360665988</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-453.6099999999997</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.80211e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-48.567</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>14.608167240558</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.66522662564525</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.008x + -35428.551</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.882918239440259e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4672.725282587521</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000002507e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8087848065452319</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-435.1800000000003</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.82544e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-48.967</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>15.14127172719298</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.86871943114794</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.309x + -36175.269</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.785911820519718e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4609.564847509468</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001052e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8091249309560957</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-431.1099999999997</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.84556e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-49.259</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>15.34263579282131</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.83733868426059</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.261x + -35522.528</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.512958789529411e-14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4548.653427379078</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8095879668986358</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-425.0100000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.86731e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-49.625</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>15.72173728566966</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.94915692257044</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.434x + -35721.389</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.021074950856468e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4484.324940651881</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000371e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8100908340196769</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-412.2200000000003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.88939e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-50.028</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>16.26011337991787</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.07914990096505</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.642x + -36072.531</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.188498569151061e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4424.978989228639</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8105762615674238</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-402.3999999999996</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.90917e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-50.36</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>16.73340161009176</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.17130054371817</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.796x + -36233.456</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.254785065452177e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4369.449685422155</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.00000000000007e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8110567516666166</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-390.1900000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.93086e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-50.671</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>17.38757418647492</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.25958601377849</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.948x + -36370.508</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.309381043340392e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4315.36498574599</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000065e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8115190168195022</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-382.6500000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.95041e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-51.032</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>17.90304276001829</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.36048756149569</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.127x + -36607.148</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.498589118958575e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4262.919131796325</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8119630862388107</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-378.8399999999997</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.96802e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-51.332</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>18.25666487588592</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.40924205617722</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.216x + -36528.559</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.024938271445678e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4212.695729862809</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000004813e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8123703030991987</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-365.6000000000004</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.98836e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-51.673</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>18.94595896029977</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.53450894203473</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.451x + -36972.104</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.191183304021579e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4162.294867322231</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8127839561811888</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-356.8899999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.00852e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-51.964</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>19.51235465091213</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.62370194794056</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.626x + -37168.634</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.418482124898383e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4111.877337241065</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8132144959811992</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-364.4500000000003</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.02758e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-52.304</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>15.50370929541121</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.27286173511095</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 9.971x + -34304.692</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.024354633209548e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4060.130789794031</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.81364901346205</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-339.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.04808e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-52.658</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>20.87295949239331</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.76551022410108</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.915x + -37301.540</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.766698240717566e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4010.225018695057</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8140807241086134</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-333.7599999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.06785e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-52.991</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>21.39762930918475</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.80641334386225</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 11.002x + -37154.576</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.042463000883891e-13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3959.688198823024</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.814478391904003</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-318.6100000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.08854e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-53.335</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>21.83364544144668</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.93313252494067</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.278x + -37672.849</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.477213977656566e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3910.339024993793</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000343e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8149153025591613</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-558.4099999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.5612e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-45.331</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>15.0310300461666</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.72664299697367</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.835x + -35506.156</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.12796442330429e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5366.106587401639</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000091e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8088070759839333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-492.3800000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.6412e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-46.781</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>18.5200798551464</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.45018396805719</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.710x + -37843.310</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.358630500636043e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5154.893764619088</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.809017651534121</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-471.1000000000004</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.66899e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-47.341</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>20.23683412513885</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.68792909302806</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.040x + -38703.556</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.33898490965731e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5079.133315690301</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000019748e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8089965631540122</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-491.3699999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.6875e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-47.721</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>14.40960569067956</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.24555651191511</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 8.443x + -35519.924</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.871717218986488e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5016.833931319816</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000473e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8090451676681393</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-466.4000000000005</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.70957e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-48.097</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>15.1131133049488</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.44265815173911</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.699x + -36190.540</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.093700857085619e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4954.367840392837</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000003275e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8092245287528519</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-461.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.72971e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-48.489</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>15.45599306280174</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.57892415878389</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.886x + -36524.158</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.99309243042633e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4887.203761068454</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000115e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8094735514605903</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-443.0100000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.75369e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-48.893</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>16.19032774773004</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.7116590316339</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.075x + -36822.258</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>650.5487553003969</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7497.600182374447</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.896013854493883e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6855287203074113</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-440.8800000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.7728e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-49.237</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>16.24302094865443</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.71423399951321</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.079x + -36337.105</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>184.2010763089851</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5533.965751206717</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.582626604446298e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7839882108766388</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-427.6999999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.79443e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-49.658</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>16.83378614114573</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.85573421623462</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.289x + -36714.106</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.567484888076167e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4685.989113430082</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000092e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8104928039472312</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-434.6099999999997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8175e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-50.033</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>13.90803128602063</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.48477089804317</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 8.756x + -33994.718</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.794987213779631e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4621.200738719145</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000004072e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8108777018965129</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-410.0100000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.83656e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-50.371</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>17.98196437562652</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.0785928196879</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.642x + -37175.120</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.828000112801305e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4558.900484609763</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000346e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8112653754793739</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-415.9300000000003</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.85874e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-50.774</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>14.37319965398693</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.69654979193359</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.053x + -34276.112</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.572115893842794e-13</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4497.35942103051</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000159e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8116577542617355</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-381.1999999999998</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.87932e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-51.11</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>19.20433361350165</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.31168193516385</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 10.039x + -37789.899</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.479636554324082e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4439.712303933526</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8120446426356559</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-373.1199999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.89853e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-51.496</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>20.14332553291304</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.39116649556614</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.183x + -37870.032</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.375642885466738e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4383.329264891176</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000005306e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.812428830684918</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-380.6500000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.91801e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-51.832</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>15.60972795033373</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.97686133854846</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.478x + -34652.049</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.404954652065036e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4330.319985182471</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8128086311006061</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-361.1599999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.93455e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-52.127</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>20.85235440915597</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.50346105919323</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.392x + -37780.096</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.805415153796025e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4277.167962881332</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000001209e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8131974903074185</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-341.77</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.95506e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-52.523</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>21.40378696546818</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.63813794159394</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.655x + -38311.153</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.816701101113977e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4225.68020968566</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000236e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8135718897118427</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-337.48</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.97261e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-52.844</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>22.45215955388193</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.6811582945821</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.741x + -38188.802</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.585499830558922e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4173.986103237598</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8139774663687427</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-345.8899999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.99104e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-53.179</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>16.76499505051395</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.25899329115317</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 9.947x + -34785.644</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.676181817938063e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4125.638854984247</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000074e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8143644785805048</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-323.6399999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.0079e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>23.49744184837182</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.77017836492048</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 10.925x + -37980.339</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.086950797531119e-11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4076.108843503315</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8147748975940801</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-332.1100000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.02506e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-53.808</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>17.52241765468649</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.38551302541805</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.172x + -34801.374</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>6.308114886164615e-11</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4028.681288404756</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000092e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8151759808052893</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-673.3800000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.3433e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-41.278</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>11.44368312097271</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.31446272005796</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 6.546x + -33908.249</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.773369087015149e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6198.61381657695</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000032e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8040028227579187</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-552.8099999999995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.48859e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-43.919</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>15.49849261970947</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.70393722633528</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 7.810x + -37342.425</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>156.042014252076</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6514.737963471643</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.209396741567813e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7964512962481898</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-514.8500000000004</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.52935e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-44.79</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>17.38330501459494</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.19171774068232</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 8.376x + -39228.452</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4680663796222e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5616.510786829333</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000004387e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8048807753810505</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-523.4400000000005</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.55537e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-45.359</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>13.30547411224578</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82.81304942244023</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 7.930x + -36398.259</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.579283410508503e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5530.186415061746</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000092e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8049181881450256</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-499.2000000000007</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.58011e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-45.878</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>13.95852331977535</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.05496310693914</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.209x + -37195.258</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.603317284057943e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5454.423793637969</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.805033876573387</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-466.7999999999993</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.59869e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-46.282</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>21.21503680336486</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.74978905742475</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.131x + -41148.045</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.237446971533636e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5384.623461030998</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8051992568463125</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-474.1599999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.61974e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-46.704</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>15.11594356413414</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.36175377562427</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 8.593x + -38066.116</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.226689218033267e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5321.314083503124</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000038e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8053495063283032</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-437.9499999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.63933e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-47.12</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>24.38722278983116</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.0403199522016</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.579x + -42205.134</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.845792840786033e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5254.874295491088</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000311e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8055457452000657</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-425.3099999999995</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.66272e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-47.557</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>26.05072463768106</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.16186385650765</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.780x + -42507.325</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.981389056793171e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5177.108304428417</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000688e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8059362765950355</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-439.3800000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.68759e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-48.046</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>17.06479299759508</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.71622665835828</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.081x + -38649.885</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.774713737377208e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5095.103051767225</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8063529036980399</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-519.5100000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.52218e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-45.106</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>18.00217835867335</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.17469698419453</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.355x + -39299.065</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.069907534395023e-13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5593.969796945806</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8049024268794357</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-455.1700000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.60818e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-46.522</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>22.51937854994964</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.80366967622841</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.211x + -41296.084</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.221061602838329e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5346.799711738155</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8051394655434512</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-439.46</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.63931e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-47.033</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>24.24965508967681</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.96642383239387</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.461x + -41659.461</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.61331280170005e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5248.361855837228</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000191e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.80523034530015</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-451.6599999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.66188e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-47.364</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>16.15813650914068</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.58381469756419</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 8.893x + -38458.596</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.237636322988008e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5179.071598703818</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8052917240031265</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-440.2300000000005</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.67974e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-47.635</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>16.32558821272281</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.63188299184445</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.960x + -38333.225</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>687.2649043276917</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7876.261885796946</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.196377565436605e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6879012776606778</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-426.04</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.69672e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-47.96</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>17.27597322471903</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.76769679345638</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.157x + -38832.080</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.274752003741324e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5075.11129026428</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8055204256242628</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-424.8000000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.7081e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-48.174</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>17.2095554225564</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.80532224603695</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.213x + -38781.635</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>675.6926825815557</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7672.482060935306</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.042145618269329e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6897216220345697</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-419.6899999999996</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.72051e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-48.389</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>17.26986756639755</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.85535644467508</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.289x + -38779.098</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.391739878458362e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4986.619782269207</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001939e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8059907920804543</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-406.7399999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.73961e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-48.749</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>18.05037081209004</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.99973577554013</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.514x + -39322.990</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.774413729136269e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4932.622675782123</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000002892e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8062673177847159</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-405.6199999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.75608e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-49.076</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>18.48516891355785</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.0257924955482</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.556x + -39068.104</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.544589170526924e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4875.627754704237</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8065856094063066</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-392.79</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.77166e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-49.307</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>18.91621684071284</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.10057947488237</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.678x + -39226.150</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.146770044696212e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4825.287805579448</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.00000000000032e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8068792654099258</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-378.3500000000004</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.79103e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-49.685</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>19.68131229438005</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.260153402963</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.949x + -39905.211</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.282712548236936e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4772.860860209185</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000006474e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8071776998594232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-372.2200000000003</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.80806e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-49.988</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>20.31622463447318</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.28748019314571</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.997x + -39670.480</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.96436503466744e-11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4720.068396756349</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000695e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8075357277893401</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-367.0299999999997</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.82497e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-50.289</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>20.56576498445174</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.30484927208443</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.027x + -39362.172</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.223557271580338e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4668.477725603038</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.00000000003895e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8078962670480704</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-349.77</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.84262e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-50.592</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>21.26285072820864</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.45841274152961</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.307x + -40108.511</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.794250209153397e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4618.882575235939</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000005248e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8082643607833156</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-343.4400000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.86058e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-50.93</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>21.79918533466964</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.53228005635252</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.447x + -40216.603</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.190897162003965e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4566.912528205035</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000057676e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8086129454663668</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-336.0599999999995</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.87802e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-51.219</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>22.33795075991537</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.53446649313155</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.451x + -39780.265</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.50755715247912e-15</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4513.390920273878</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8089968884469032</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-351.2399999999998</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.89428e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-51.509</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>16.5873207785795</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.18369144018486</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 9.817x + -36818.620</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.652601395390524e-13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4466.6218191977</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8093410601953002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-323.6199999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.91044e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-51.811</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>23.41962540093693</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.674280430401</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.727x + -40027.942</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.337863568645199e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4417.126726544804</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8097070672747861</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-328.48</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.92914e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-52.162</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>17.46920675768397</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.26655942492778</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 9.960x + -36600.308</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.279026472579868e-11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4369.706001322709</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000139e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8100372056077293</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-316.8399999999997</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.94327e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-52.405</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>17.33897899506804</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.38469541083499</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.171x + -37075.512</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.252783642140035e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4327.200546711805</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8103166560932665</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-786.3800000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.25118e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-40.099</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>9.394295933734938</v>
+      </c>
+      <c r="K2" t="n">
+        <v>80.13042958801027</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 5.748x + -31288.804</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>191.3727882650652</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7531.255893526579</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.423198283725921e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7814442485267088</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-604.1199999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.48536e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-43.798</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>13.01248431204167</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.17326873583082</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 7.275x + -34444.151</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.753490218562992e-14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5662.921373613473</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.802973592959172</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-553.4099999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.55454e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-45.009</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>15.1670189462357</v>
+      </c>
+      <c r="K4" t="n">
+        <v>82.74117226700031</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 7.851x + -35796.285</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.077429156655222e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5453.727257515189</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000002162e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.803262844252645</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-551.8999999999996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.58499e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-45.66</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>12.03981613480791</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82.5290597509531</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 7.626x + -34021.325</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.005883091006426e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5362.1644611844</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000007036e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8033355543271683</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-509.8599999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.61178e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-46.197</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>17.53207979215273</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.2510287803043</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.450x + -37351.454</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.237157387013213e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5276.59588906396</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8034770935342315</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-515.4700000000003</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.63544e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-46.666</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>13.25803056456122</v>
+      </c>
+      <c r="K7" t="n">
+        <v>82.97500168609544</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.115x + -35221.656</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.604080970376257e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5206.980093308081</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8035625101739978</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-506.7699999999995</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.65559e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-47.068</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>13.5829170505562</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.09803310922877</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 8.261x + -35418.582</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.084588044883743e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5136.521880209947</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000003492e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8036779379475766</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-499.0699999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.677e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-47.485</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>13.93554259462145</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.17173065770778</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 8.351x + -35334.282</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.606270498379967e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5066.026369261791</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000447e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8038827089769069</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-481.4499999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.69951e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-47.947</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>14.55847708675547</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.38136499317879</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 8.618x + -36014.240</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.196625497896767e-12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4997.020269697509</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000068e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8040937518529033</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-467.5900000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.72019e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-48.327</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>15.01479427738284</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.54570271975417</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 8.840x + -36521.777</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.323720389410133e-16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4934.457911713206</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8042951503994878</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-544.6599999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.59485e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-46.179</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>12.86477216881484</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.52109144520348</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.617x + -33825.262</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.055618607895975e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5290.061734678266</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8071831602017653</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-488.1199999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.6696e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-47.423</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>14.57792595133182</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.12115752574971</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.289x + -35330.390</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.705137972537033e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5085.916792003528</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000114e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8074555933992739</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-535.0299999999997</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.68079e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-46.195</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>12.09366052104749</v>
+      </c>
+      <c r="K4" t="n">
+        <v>82.47129281171165</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 7.566x + -31714.008</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.438550148681307e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5010.869416476461</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000049e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8073918471191233</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-514.3500000000004</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.70118e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-47.403</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>13.20636472211435</v>
+      </c>
+      <c r="K5" t="n">
+        <v>82.89206290115872</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 8.019x + -33265.953</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>189.6482019792596</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5750.296419847661</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.508954410429453e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7848445644307727</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-502.5799999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.71893e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-48.054</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>13.89732550783002</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.10402741295749</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.268x + -33949.974</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.72424720933545e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4893.829684938073</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8075964988756094</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-484.0099999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.73724e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-48.511</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>14.3478228818373</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.32672811666143</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 8.547x + -34750.439</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>649.425138428979</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7372.658546923845</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.475419789424068e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6876430145591385</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-473.5200000000004</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.75619e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-48.921</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>15.09443033640177</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.40435490877876</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 8.649x + -34773.630</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.370902254011373e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4781.129777845021</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000141e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8080085470697375</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-459.48</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.7739e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-49.34</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>15.62548392320535</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.59096597364272</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 8.903x + -35449.251</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.116457575384542e-15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4729.892920735024</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.808261652846059</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-448.7499999999995</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.78938e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-49.613</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>16.05623046813602</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.68642399134255</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.038x + -35666.334</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.35953818672846e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4682.741197291212</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8085001208036428</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-436.1500000000005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.80722e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-49.965</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>16.61470356845302</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.77792868091885</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.172x + -35831.694</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.326588828358574e-13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4634.452873220527</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8087611793457558</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-428.0999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.8242e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-50.287</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>17.25876927724666</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.88800939870723</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.339x + -36136.988</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.293114410044997e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4586.643044613477</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8090690648313822</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-440.9999999999995</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.8382e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-50.58</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>13.85386495884802</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.45699752787648</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 8.719x + -33245.819</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.018720049496159e-13</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4541.795260246833</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8093593177940723</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-403.79</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.8567e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-50.909</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>18.51279254801508</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.10289220001455</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.682x + -36799.361</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.540312836456596e-11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4496.128594752121</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8096784928035938</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-396.1499999999996</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.87101e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-51.177</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>18.90119876416458</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.19604431606372</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 9.838x + -37066.466</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.36046322035644e-11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4452.563090708637</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8100186285118254</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-385.6400000000003</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.88897e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-51.494</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>19.81287643206559</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.21914493275732</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.878x + -36823.196</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.021803329851366e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4405.087504053349</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8104016452869768</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-375.0599999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.90441e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-51.759</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>20.12314980608045</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.33781370364011</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.086x + -37281.299</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.937037436539442e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4361.65046224517</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000063e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8107539240976714</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-366.5300000000002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.92083e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-52.122</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>20.9041634364756</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.40761872586336</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.213x + -37364.847</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.117002960450743e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4315.182614029754</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000085e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8111452148672141</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-355.79</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.93752e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-52.381</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>21.02127507645956</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.54463486312633</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.471x + -37950.206</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.126596720750614e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4266.882086286062</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.00000000000008e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8115357865053381</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-363.0699999999997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.95656e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-52.715</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>16.41849353776825</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.07251735048182</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 9.632x + -34332.363</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.679406849722052e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4220.201840364709</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8119171583145481</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-352.9500000000003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.97413e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-53.069</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>16.63627543716687</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.15570547181306</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 9.770x + -34458.292</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.817174536290988e-13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4171.953804259084</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8123083885485469</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-321.73</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.99301e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-53.407</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>23.46829742862839</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.72584081309704</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.833x + -37994.633</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.568152257954956e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4121.861361445171</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000077e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8127145675821018</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-611.04</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.51106e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-44.79</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>13.43471566757038</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.1562512184141</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.259x + -33687.626</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.942065437854256e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5477.383319260361</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8066979688796725</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-503.1899999999996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.66723e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-47.577</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>13.86787334528728</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.10185929516959</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.266x + -35133.673</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.031921924648365e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5070.109834270832</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001138e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8074867789163644</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-465.2200000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.71e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-48.353</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>15.31115103594255</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.49676447950537</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 8.772x + -36478.518</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.302392021020318e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4958.757284769948</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000359e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8075947764287479</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-455.7699999999995</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.73286e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-48.774</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>15.70696494171544</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.60648730402283</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 8.924x + -36588.038</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.760648399349517e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4885.252140003793</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8076948882266216</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-440.8499999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.75587e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-49.169</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>16.49706824122366</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.79580925818351</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.199x + -37245.367</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.347109086816492e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4817.172109067823</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.807842333571815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-424.3200000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.77914e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-49.54</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>16.86467725316609</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.9055863514142</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.366x + -37423.539</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.922653631191028e-14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4749.530399016374</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000084e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8080730103820181</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-417.2799999999997</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.80104e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-49.932</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>17.37990044554744</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.99388639422426</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.505x + -37456.408</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.066068112178194e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4679.990620401043</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8082814636921926</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-408.9400000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.82413e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-50.305</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>18.06210329273584</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.10967997467304</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.693x + -37692.058</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.491441902219318e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4613.543397317023</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8085463624656438</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-388.1700000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.84824e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-50.734</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>18.95957078803052</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.26331272428541</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.954x + -38196.749</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.149180429125523e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4547.565266176706</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000723e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8088080455121895</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-396.6400000000003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.87218e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-51.054</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>14.76262252789807</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.84734453332298</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.277x + -34924.616</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.757646146159926e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4482.094117434618</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000152e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.809134176417303</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-522.9899999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.60268e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-46.503</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>13.38630069582832</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.87393119718224</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.999x + -35459.499</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.578942527089263e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5279.715469654875</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8067717763134378</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-442.1999999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.68472e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-47.812</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>23.10307683492782</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.03745304966596</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.575x + -40804.695</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.415940276857433e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5056.057124311519</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8071035404653313</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-458.5500000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.7086e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-48.228</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>15.37265328472532</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.57990271081528</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 8.887x + -37058.260</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.130217462671344e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4977.812928261335</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8071761758645469</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-451.4300000000003</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.72934e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-48.532</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>15.78167946170823</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.67438909756599</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.021x + -37157.894</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.926527047309575e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4912.408834477734</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000487e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8072454806599807</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-441.2400000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.75009e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-48.856</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>16.10817675846645</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.75956336589456</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.145x + -37200.921</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.378547265192882e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4848.606570220082</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001022e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.807409318328756</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-431.27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.76893e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-49.18</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>16.53217364605438</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.81086574206168</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.221x + -37106.558</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.755685527576211e-18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4790.674496682132</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8075889670311244</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-424.2600000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.78711e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-49.476</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>16.98964163318965</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.92959836304219</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.403x + -37421.762</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.561718769437166e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4732.368596217309</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000002686e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8078455554381277</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-408.3199999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.81076e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-49.801</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>17.91389735774602</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.0364600879557</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.573x + -37628.805</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.860075500833695e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4667.655583209818</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8082400289425073</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-397.8800000000006</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.83017e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-50.148</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>18.25058310280341</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.12534175077576</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.719x + -37753.357</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.346757406467763e-13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4607.999201860185</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8085682225187025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-388.2600000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.85024e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-50.424</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>18.69381357353614</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.22603129537485</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.890x + -38003.530</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.234129074521629e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4555.82157803937</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000521e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.808902558109087</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-395.27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.86781e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-50.747</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>14.82921385743929</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.90872562169774</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.371x + -35480.366</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.352918440935144e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4504.749585845556</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000001008e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.809240006452921</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-371.7999999999997</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.88562e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-51.017</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>19.75701487335977</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.40688141823696</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 10.211x + -38441.928</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.699898045402136e-11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4455.872518916538</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000155e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8095311796080122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-361.71</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.90275e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-51.275</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>20.12452664506975</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.4674747761381</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 10.324x + -38484.187</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.353173624462726e-12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4407.312585899738</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000163e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8099136097304149</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-345.4099999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.9224e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-51.623</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>21.34151722038827</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.58105577661149</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.542x + -38904.051</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.89790878882165e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4358.651490445566</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000002352e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8102875653768605</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-340.48</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.93855e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-51.936</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>21.43725027530183</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.59460595253761</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.568x + -38576.844</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>8.05632159524709e-13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4308.860573263448</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.810692114901571</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-331.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.95844e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-52.269</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>22.63846341325704</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.71730927802568</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.815x + -39053.927</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.630101072426787e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4258.310975849784</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000098e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.811065112569949</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-340.1800000000003</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.975e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-52.492</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>16.75243874884691</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.26213368622977</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 9.952x + -35406.247</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.653147173285814e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4215.906234041012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000035e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8113631187800701</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-332.73</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.99353e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-52.823</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>17.20255660506453</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.31321274463423</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.042x + -35335.578</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.741472560869826e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4165.342381465651</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000038e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8117937530981963</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-321.9000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.01235e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-53.121</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>17.20407134501571</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.43396423022563</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.261x + -35730.553</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.933566329209869e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4116.21004738066</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000058e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8121803896503114</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-312.7600000000002</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.03047e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-53.453</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>17.98711265336727</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.4956791147991</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 10.377x + -35747.032</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.496179118674745e-10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4068.479807315798</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000158e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8125686706926736</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-305.6399999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.04658e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-53.714</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>17.86273357951013</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.52793968489024</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.439x + -35584.732</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.071552598642541e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4024.86388408256</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000174e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8129413408136722</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-366.8599999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.16796e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-55.217</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>15.91567484102823</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.53348328843273</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.449x + -32236.996</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.272466868428998e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3619.454970916422</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000035e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8108572163218742</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-358.8599999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.18813e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-55.418</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>14.37902595757237</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.37982734991574</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.162x + -31024.588</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.59725507536361e-13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3592.977572070574</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000019e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8108532467440325</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-337.23</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.21057e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-55.818</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>15.01739136523552</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.5056097899139</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.396x + -31406.859</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.798435387751001e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3549.577884851644</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8110341294277318</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-327.6999999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.2363e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-56.321</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>15.4148460142573</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.60013880773768</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.579x + -31402.327</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.708585652094037e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3476.110299697852</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000002916e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8114105672819329</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-317.9200000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.27372e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-56.995</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04353982300885002</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6706910907576755</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.508337171810209</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.604150637780972</v>
+      </c>
+      <c r="J6" t="n">
+        <v>55.59163245080001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.47962002859148</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.347x + -29914.606</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.373108012083583e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3397.295857059149</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8117553379260558</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-302.6900000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.30685e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-57.591</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1492251595259892</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6786564030791061</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.451282051282011</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.70556495979688</v>
+      </c>
+      <c r="J7" t="n">
+        <v>65.73830962343008</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.59450199479052</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.568x + -29911.338</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.554197580282301e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3316.466220036885</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000005e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8121593380145607</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-283.96</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.34173e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-58.183</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>17.22958352770715</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.00495021019583</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.441x + -31741.590</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.110356629220958e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3230.539140002104</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.812681234647441</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-275.7199999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.38033e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-58.914</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01820208023773193</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7697466467958303</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.838346253230073</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.758596795149455</v>
+      </c>
+      <c r="J9" t="n">
+        <v>94.85838764180468</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.83112068714424</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.055x + -29779.754</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.473947042753324e-14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3144.604814122403</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8132741061941047</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-255.48</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.41739e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-59.546</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3303630363036422</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.878561354019778</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.889866666666707</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.731990572101985</v>
+      </c>
+      <c r="J10" t="n">
+        <v>127.2110103626955</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.96047525913518</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.340x + -29821.954</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.364170239848895e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3064.205932408323</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000038e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8139179823338086</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-256.1700000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.44954e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-60.137</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.286054827175232</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7265398550724489</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.26284558327713</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.044564860426918</v>
+      </c>
+      <c r="J11" t="n">
+        <v>33.77918030928299</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.71565001313172</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.812x + -27664.320</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.400856975976487e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2985.807381026741</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000002247e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.814566307395075</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-609.7700000000004</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-569.1500000000005</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-509.29</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-484.1499999999996</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-472.3000000000002</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-456.46</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-466.8000000000002</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-461.8400000000001</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-446.4000000000001</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-428.7399999999998</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-673.3800000000001</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-552.8099999999995</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-514.8500000000004</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-523.4400000000005</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-499.2000000000007</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-466.7999999999993</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-474.1599999999999</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-437.9499999999998</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-425.3099999999995</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-439.3800000000001</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-786.3800000000001</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-604.1199999999999</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-553.4099999999999</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-551.8999999999996</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-509.8599999999997</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-515.4700000000003</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-506.7699999999995</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-499.0699999999997</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-481.4499999999998</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-467.5900000000001</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-611.04</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-503.1899999999996</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-465.2200000000003</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-455.7699999999995</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-440.8499999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-424.3200000000002</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-417.2799999999997</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-408.9400000000001</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-388.1700000000001</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-396.6400000000003</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-366.8599999999997</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-358.8599999999997</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-337.23</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-327.6999999999998</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-317.9200000000001</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-302.6900000000001</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-283.96</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-275.7199999999998</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-255.48</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-256.1700000000001</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-609.7700000000004</v>
+        <v>4410.893</v>
       </c>
       <c r="D2" t="n">
         <v>1.49611e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-569.1500000000005</v>
+        <v>4194.489</v>
       </c>
       <c r="D3" t="n">
         <v>1.56976e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-509.29</v>
+        <v>4157.799</v>
       </c>
       <c r="D4" t="n">
         <v>1.59836e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-484.1499999999996</v>
+        <v>4100.618</v>
       </c>
       <c r="D5" t="n">
         <v>1.6234e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-472.3000000000002</v>
+        <v>4025.463</v>
       </c>
       <c r="D6" t="n">
         <v>1.65025e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-456.46</v>
+        <v>3964.407</v>
       </c>
       <c r="D7" t="n">
         <v>1.67483e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-466.8000000000002</v>
+        <v>3877.833</v>
       </c>
       <c r="D8" t="n">
         <v>1.69992e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-461.8400000000001</v>
+        <v>3817.962</v>
       </c>
       <c r="D9" t="n">
         <v>1.72076e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-446.4000000000001</v>
+        <v>3767.345</v>
       </c>
       <c r="D10" t="n">
         <v>1.74308e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-428.7399999999998</v>
+        <v>3714.126</v>
       </c>
       <c r="D11" t="n">
         <v>1.76688e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-525.6799999999994</v>
+        <v>4076.877</v>
       </c>
       <c r="D2" t="n">
         <v>1.62054e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-514.4899999999998</v>
+        <v>3884.529</v>
       </c>
       <c r="D3" t="n">
         <v>1.68724e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-492.6700000000001</v>
+        <v>3820.036</v>
       </c>
       <c r="D4" t="n">
         <v>1.71526e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-460.7600000000002</v>
+        <v>3792.666</v>
       </c>
       <c r="D5" t="n">
         <v>1.73552e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-469.7600000000002</v>
+        <v>3713.832</v>
       </c>
       <c r="D6" t="n">
         <v>1.75917e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-462.7399999999998</v>
+        <v>3663.06</v>
       </c>
       <c r="D7" t="n">
         <v>1.77969e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-453.6099999999997</v>
+        <v>3610.714</v>
       </c>
       <c r="D8" t="n">
         <v>1.80211e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-435.1800000000003</v>
+        <v>3563.327</v>
       </c>
       <c r="D9" t="n">
         <v>1.82544e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-431.1099999999997</v>
+        <v>3515.496</v>
       </c>
       <c r="D10" t="n">
         <v>1.84556e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-425.0100000000002</v>
+        <v>3465.324</v>
       </c>
       <c r="D11" t="n">
         <v>1.86731e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-412.2200000000003</v>
+        <v>3416.541</v>
       </c>
       <c r="D12" t="n">
         <v>1.88939e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-402.3999999999996</v>
+        <v>3376.836</v>
       </c>
       <c r="D13" t="n">
         <v>1.90917e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-390.1900000000001</v>
+        <v>3334.832</v>
       </c>
       <c r="D14" t="n">
         <v>1.93086e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-382.6500000000001</v>
+        <v>3290.723</v>
       </c>
       <c r="D15" t="n">
         <v>1.95041e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-378.8399999999997</v>
+        <v>3250.783</v>
       </c>
       <c r="D16" t="n">
         <v>1.96802e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-365.6000000000004</v>
+        <v>3214.116</v>
       </c>
       <c r="D17" t="n">
         <v>1.98836e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-356.8899999999999</v>
+        <v>3173.643</v>
       </c>
       <c r="D18" t="n">
         <v>2.00852e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-364.4500000000003</v>
+        <v>3118.426</v>
       </c>
       <c r="D19" t="n">
         <v>2.02758e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-339.25</v>
+        <v>3093.033</v>
       </c>
       <c r="D20" t="n">
         <v>2.04808e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-333.7599999999998</v>
+        <v>3051.838</v>
       </c>
       <c r="D21" t="n">
         <v>2.06785e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-318.6100000000001</v>
+        <v>3016.932</v>
       </c>
       <c r="D22" t="n">
         <v>2.08854e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-558.4099999999999</v>
+        <v>4238.991</v>
       </c>
       <c r="D2" t="n">
         <v>1.5612e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-492.3800000000001</v>
+        <v>4044.713</v>
       </c>
       <c r="D3" t="n">
         <v>1.6412e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-471.1000000000004</v>
+        <v>3976.748</v>
       </c>
       <c r="D4" t="n">
         <v>1.66899e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-491.3699999999999</v>
+        <v>3898.464</v>
       </c>
       <c r="D5" t="n">
         <v>1.6875e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-466.4000000000005</v>
+        <v>3854.403</v>
       </c>
       <c r="D6" t="n">
         <v>1.70957e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-461.5</v>
+        <v>3796.718</v>
       </c>
       <c r="D7" t="n">
         <v>1.72971e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-443.0100000000002</v>
+        <v>3744.883</v>
       </c>
       <c r="D8" t="n">
         <v>1.75369e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-440.8800000000001</v>
+        <v>3689.536</v>
       </c>
       <c r="D9" t="n">
         <v>1.7728e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-427.6999999999998</v>
+        <v>3638.875</v>
       </c>
       <c r="D10" t="n">
         <v>1.79443e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-434.6099999999997</v>
+        <v>3564.946</v>
       </c>
       <c r="D11" t="n">
         <v>1.8175e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-410.0100000000002</v>
+        <v>3535.694</v>
       </c>
       <c r="D12" t="n">
         <v>1.83656e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-415.9300000000003</v>
+        <v>3467.038</v>
       </c>
       <c r="D13" t="n">
         <v>1.85874e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-381.1999999999998</v>
+        <v>3445.639</v>
       </c>
       <c r="D14" t="n">
         <v>1.87932e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-373.1199999999999</v>
+        <v>3399.821</v>
       </c>
       <c r="D15" t="n">
         <v>1.89853e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-380.6500000000001</v>
+        <v>3340.591</v>
       </c>
       <c r="D16" t="n">
         <v>1.91801e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-361.1599999999999</v>
+        <v>3315.161</v>
       </c>
       <c r="D17" t="n">
         <v>1.93455e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-341.77</v>
+        <v>3277.023</v>
       </c>
       <c r="D18" t="n">
         <v>1.95506e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-337.48</v>
+        <v>3235.415</v>
       </c>
       <c r="D19" t="n">
         <v>1.97261e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-345.8899999999999</v>
+        <v>3178.289</v>
       </c>
       <c r="D20" t="n">
         <v>1.99104e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-323.6399999999999</v>
+        <v>3156.465</v>
       </c>
       <c r="D21" t="n">
         <v>2.0079e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-332.1100000000001</v>
+        <v>3101.983</v>
       </c>
       <c r="D22" t="n">
         <v>2.02506e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-673.3800000000001</v>
+        <v>4912.635</v>
       </c>
       <c r="D2" t="n">
         <v>1.3433e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-552.8099999999995</v>
+        <v>4498.614</v>
       </c>
       <c r="D3" t="n">
         <v>1.48859e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-514.8500000000004</v>
+        <v>4393.312</v>
       </c>
       <c r="D4" t="n">
         <v>1.52935e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-523.4400000000005</v>
+        <v>4294.186</v>
       </c>
       <c r="D5" t="n">
         <v>1.55537e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-499.2000000000007</v>
+        <v>4235.998</v>
       </c>
       <c r="D6" t="n">
         <v>1.58011e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-466.7999999999993</v>
+        <v>4203.937</v>
       </c>
       <c r="D7" t="n">
         <v>1.59869e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-474.1599999999999</v>
+        <v>4128.549</v>
       </c>
       <c r="D8" t="n">
         <v>1.61974e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-437.9499999999998</v>
+        <v>4100.611</v>
       </c>
       <c r="D9" t="n">
         <v>1.63933e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-425.3099999999995</v>
+        <v>4037.859</v>
       </c>
       <c r="D10" t="n">
         <v>1.66272e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-439.3800000000001</v>
+        <v>3944.908</v>
       </c>
       <c r="D11" t="n">
         <v>1.68759e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-519.5100000000002</v>
+        <v>4402.141</v>
       </c>
       <c r="D2" t="n">
         <v>1.52218e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-455.1700000000001</v>
+        <v>4176.882000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.60818e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-439.46</v>
+        <v>4089.772</v>
       </c>
       <c r="D4" t="n">
         <v>1.63931e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-451.6599999999999</v>
+        <v>4007.653</v>
       </c>
       <c r="D5" t="n">
         <v>1.66188e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-440.2300000000005</v>
+        <v>3963.018</v>
       </c>
       <c r="D6" t="n">
         <v>1.67974e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-426.04</v>
+        <v>3922.402</v>
       </c>
       <c r="D7" t="n">
         <v>1.69672e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-424.8000000000002</v>
+        <v>3890.286</v>
       </c>
       <c r="D8" t="n">
         <v>1.7081e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-419.6899999999996</v>
+        <v>3858.541</v>
       </c>
       <c r="D9" t="n">
         <v>1.72051e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-406.7399999999998</v>
+        <v>3812.463</v>
       </c>
       <c r="D10" t="n">
         <v>1.73961e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-405.6199999999999</v>
+        <v>3763.779</v>
       </c>
       <c r="D11" t="n">
         <v>1.75608e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-392.79</v>
+        <v>3730.284</v>
       </c>
       <c r="D12" t="n">
         <v>1.77166e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-378.3500000000004</v>
+        <v>3690.293</v>
       </c>
       <c r="D13" t="n">
         <v>1.79103e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-372.2200000000003</v>
+        <v>3645.16</v>
       </c>
       <c r="D14" t="n">
         <v>1.80806e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-367.0299999999997</v>
+        <v>3601.341</v>
       </c>
       <c r="D15" t="n">
         <v>1.82497e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-349.77</v>
+        <v>3569.599</v>
       </c>
       <c r="D16" t="n">
         <v>1.84262e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-343.4400000000001</v>
+        <v>3526.349</v>
       </c>
       <c r="D17" t="n">
         <v>1.86058e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-336.0599999999995</v>
+        <v>3485.29</v>
       </c>
       <c r="D18" t="n">
         <v>1.87802e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-351.2399999999998</v>
+        <v>3424.659</v>
       </c>
       <c r="D19" t="n">
         <v>1.89428e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-323.6199999999999</v>
+        <v>3407.722</v>
       </c>
       <c r="D20" t="n">
         <v>1.91044e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-328.48</v>
+        <v>3350.828</v>
       </c>
       <c r="D21" t="n">
         <v>1.92914e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-316.8399999999997</v>
+        <v>3324.337</v>
       </c>
       <c r="D22" t="n">
         <v>1.94327e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-786.3800000000001</v>
+        <v>5171.343</v>
       </c>
       <c r="D2" t="n">
         <v>1.25118e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-604.1199999999999</v>
+        <v>4432.228</v>
       </c>
       <c r="D3" t="n">
         <v>1.48536e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-553.4099999999999</v>
+        <v>4246.938</v>
       </c>
       <c r="D4" t="n">
         <v>1.55454e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-551.8999999999996</v>
+        <v>4145.025000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.58499e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-509.8599999999997</v>
+        <v>4097.360000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.61178e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-515.4700000000003</v>
+        <v>4014.645</v>
       </c>
       <c r="D7" t="n">
         <v>1.63544e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-506.7699999999995</v>
+        <v>3958.379</v>
       </c>
       <c r="D8" t="n">
         <v>1.65559e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-499.0699999999997</v>
+        <v>3895.914</v>
       </c>
       <c r="D9" t="n">
         <v>1.677e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-481.4499999999998</v>
+        <v>3844.036</v>
       </c>
       <c r="D10" t="n">
         <v>1.69951e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-467.5900000000001</v>
+        <v>3793.37</v>
       </c>
       <c r="D11" t="n">
         <v>1.72019e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-544.6599999999999</v>
+        <v>4136.258000000001</v>
       </c>
       <c r="D2" t="n">
         <v>1.59485e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-488.1199999999999</v>
+        <v>3952.457</v>
       </c>
       <c r="D3" t="n">
         <v>1.6696e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-535.0299999999997</v>
+        <v>3882.862</v>
       </c>
       <c r="D4" t="n">
         <v>1.68079e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-514.3500000000004</v>
+        <v>3833.271999999999</v>
       </c>
       <c r="D5" t="n">
         <v>1.70118e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-502.5799999999999</v>
+        <v>3787.416999999999</v>
       </c>
       <c r="D6" t="n">
         <v>1.71893e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-484.0099999999998</v>
+        <v>3747.302</v>
       </c>
       <c r="D7" t="n">
         <v>1.73724e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-473.5200000000004</v>
+        <v>3699.331</v>
       </c>
       <c r="D8" t="n">
         <v>1.75619e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-459.48</v>
+        <v>3657.599</v>
       </c>
       <c r="D9" t="n">
         <v>1.7739e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-448.7499999999995</v>
+        <v>3622.848</v>
       </c>
       <c r="D10" t="n">
         <v>1.78938e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-436.1500000000005</v>
+        <v>3583.788</v>
       </c>
       <c r="D11" t="n">
         <v>1.80722e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-428.0999999999999</v>
+        <v>3543.513</v>
       </c>
       <c r="D12" t="n">
         <v>1.8242e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-440.9999999999995</v>
+        <v>3487.706</v>
       </c>
       <c r="D13" t="n">
         <v>1.8382e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-403.79</v>
+        <v>3474.855</v>
       </c>
       <c r="D14" t="n">
         <v>1.8567e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-396.1499999999996</v>
+        <v>3443.096</v>
       </c>
       <c r="D15" t="n">
         <v>1.87101e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-385.6400000000003</v>
+        <v>3404.245</v>
       </c>
       <c r="D16" t="n">
         <v>1.88897e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-375.0599999999999</v>
+        <v>3373.864</v>
       </c>
       <c r="D17" t="n">
         <v>1.90441e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-366.5300000000002</v>
+        <v>3334.496</v>
       </c>
       <c r="D18" t="n">
         <v>1.92083e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-355.79</v>
+        <v>3301.107</v>
       </c>
       <c r="D19" t="n">
         <v>1.93752e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-363.0699999999997</v>
+        <v>3242.685</v>
       </c>
       <c r="D20" t="n">
         <v>1.95656e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-352.9500000000003</v>
+        <v>3205.215</v>
       </c>
       <c r="D21" t="n">
         <v>1.97413e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-321.73</v>
+        <v>3186.589</v>
       </c>
       <c r="D22" t="n">
         <v>1.99301e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-611.04</v>
+        <v>4348.036</v>
       </c>
       <c r="D2" t="n">
         <v>1.51106e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-503.1899999999996</v>
+        <v>3940.101000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.66723e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-465.2200000000003</v>
+        <v>3843.614</v>
       </c>
       <c r="D4" t="n">
         <v>1.71e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-455.7699999999995</v>
+        <v>3780.592</v>
       </c>
       <c r="D5" t="n">
         <v>1.73286e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-440.8499999999999</v>
+        <v>3728.027</v>
       </c>
       <c r="D6" t="n">
         <v>1.75587e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-424.3200000000002</v>
+        <v>3675.832</v>
       </c>
       <c r="D7" t="n">
         <v>1.77914e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-417.2799999999997</v>
+        <v>3616.231</v>
       </c>
       <c r="D8" t="n">
         <v>1.80104e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-408.9400000000001</v>
+        <v>3558.578</v>
       </c>
       <c r="D9" t="n">
         <v>1.82413e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-388.1700000000001</v>
+        <v>3509.456</v>
       </c>
       <c r="D10" t="n">
         <v>1.84824e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-396.6400000000003</v>
+        <v>3436.622</v>
       </c>
       <c r="D11" t="n">
         <v>1.87218e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-522.9899999999998</v>
+        <v>4125.245</v>
       </c>
       <c r="D2" t="n">
         <v>1.60268e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-442.1999999999998</v>
+        <v>3945.581000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.68472e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-458.5500000000002</v>
+        <v>3854.231</v>
       </c>
       <c r="D4" t="n">
         <v>1.7086e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-451.4300000000003</v>
+        <v>3798.029</v>
       </c>
       <c r="D5" t="n">
         <v>1.72934e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-441.2400000000002</v>
+        <v>3745.503</v>
       </c>
       <c r="D6" t="n">
         <v>1.75009e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-431.27</v>
+        <v>3701.435</v>
       </c>
       <c r="D7" t="n">
         <v>1.76893e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-424.2600000000002</v>
+        <v>3654.411</v>
       </c>
       <c r="D8" t="n">
         <v>1.78711e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-408.3199999999997</v>
+        <v>3604.128</v>
       </c>
       <c r="D9" t="n">
         <v>1.81076e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-397.8800000000006</v>
+        <v>3557.757</v>
       </c>
       <c r="D10" t="n">
         <v>1.83017e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-388.2600000000002</v>
+        <v>3514.675</v>
       </c>
       <c r="D11" t="n">
         <v>1.85024e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-395.27</v>
+        <v>3459.314</v>
       </c>
       <c r="D12" t="n">
         <v>1.86781e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-371.7999999999997</v>
+        <v>3436.244</v>
       </c>
       <c r="D13" t="n">
         <v>1.88562e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-361.71</v>
+        <v>3399.643</v>
       </c>
       <c r="D14" t="n">
         <v>1.90275e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-345.4099999999999</v>
+        <v>3363.146</v>
       </c>
       <c r="D15" t="n">
         <v>1.9224e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-340.48</v>
+        <v>3323.491</v>
       </c>
       <c r="D16" t="n">
         <v>1.93855e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-331.25</v>
+        <v>3280.727</v>
       </c>
       <c r="D17" t="n">
         <v>1.95844e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-340.1800000000003</v>
+        <v>3230.648</v>
       </c>
       <c r="D18" t="n">
         <v>1.975e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-332.73</v>
+        <v>3191.834</v>
       </c>
       <c r="D19" t="n">
         <v>1.99353e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-321.9000000000001</v>
+        <v>3153.2</v>
       </c>
       <c r="D20" t="n">
         <v>2.01235e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-312.7600000000002</v>
+        <v>3116.067</v>
       </c>
       <c r="D21" t="n">
         <v>2.03047e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-305.6399999999999</v>
+        <v>3083.189</v>
       </c>
       <c r="D22" t="n">
         <v>2.04658e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-366.8599999999997</v>
+        <v>2712.444</v>
       </c>
       <c r="D2" t="n">
         <v>2.16796e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-358.8599999999997</v>
+        <v>2677.859</v>
       </c>
       <c r="D3" t="n">
         <v>2.18813e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-337.23</v>
+        <v>2644.616</v>
       </c>
       <c r="D4" t="n">
         <v>2.21057e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-327.6999999999998</v>
+        <v>2589.299</v>
       </c>
       <c r="D5" t="n">
         <v>2.2363e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-317.9200000000001</v>
+        <v>2510.877</v>
       </c>
       <c r="D6" t="n">
         <v>2.27372e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-302.6900000000001</v>
+        <v>2447.341</v>
       </c>
       <c r="D7" t="n">
         <v>2.30685e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-283.96</v>
+        <v>2386.682</v>
       </c>
       <c r="D8" t="n">
         <v>2.34173e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-275.7199999999998</v>
+        <v>2304.896</v>
       </c>
       <c r="D9" t="n">
         <v>2.38033e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-255.48</v>
+        <v>2244.728</v>
       </c>
       <c r="D10" t="n">
         <v>2.41739e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-256.1700000000001</v>
+        <v>2171.918</v>
       </c>
       <c r="D11" t="n">
         <v>2.44954e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>4410.893</v>
       </c>
+      <c r="C2" t="n">
+        <v>4725.49282168417</v>
+      </c>
       <c r="D2" t="n">
         <v>1.49611e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>4194.489</v>
       </c>
+      <c r="C3" t="n">
+        <v>4519.87531865947</v>
+      </c>
       <c r="D3" t="n">
         <v>1.56976e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>4157.799</v>
       </c>
+      <c r="C4" t="n">
+        <v>4459.037660286593</v>
+      </c>
       <c r="D4" t="n">
         <v>1.59836e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>4100.618</v>
       </c>
+      <c r="C5" t="n">
+        <v>4403.495716325665</v>
+      </c>
       <c r="D5" t="n">
         <v>1.6234e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>4025.463</v>
       </c>
+      <c r="C6" t="n">
+        <v>4331.451187400209</v>
+      </c>
       <c r="D6" t="n">
         <v>1.65025e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>3964.407</v>
       </c>
+      <c r="C7" t="n">
+        <v>4267.933394411134</v>
+      </c>
       <c r="D7" t="n">
         <v>1.67483e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>3877.833</v>
       </c>
+      <c r="C8" t="n">
+        <v>4197.500593028707</v>
+      </c>
       <c r="D8" t="n">
         <v>1.69992e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>3817.962</v>
       </c>
+      <c r="C9" t="n">
+        <v>4142.219813032094</v>
+      </c>
       <c r="D9" t="n">
         <v>1.72076e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>3767.345</v>
       </c>
+      <c r="C10" t="n">
+        <v>4084.731711900554</v>
+      </c>
       <c r="D10" t="n">
         <v>1.74308e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>3714.126</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4034.098724752016</v>
       </c>
       <c r="D11" t="n">
         <v>1.76688e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>4076.877</v>
       </c>
+      <c r="C2" t="n">
+        <v>4393.72395749659</v>
+      </c>
       <c r="D2" t="n">
         <v>1.62054e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>3884.529</v>
       </c>
+      <c r="C3" t="n">
+        <v>4209.792337047694</v>
+      </c>
       <c r="D3" t="n">
         <v>1.68724e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>3820.036</v>
       </c>
+      <c r="C4" t="n">
+        <v>4143.996829012391</v>
+      </c>
       <c r="D4" t="n">
         <v>1.71526e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>3792.666</v>
       </c>
+      <c r="C5" t="n">
+        <v>4104.83708909647</v>
+      </c>
       <c r="D5" t="n">
         <v>1.73552e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>3713.832</v>
       </c>
+      <c r="C6" t="n">
+        <v>4039.035751822627</v>
+      </c>
       <c r="D6" t="n">
         <v>1.75917e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>3663.06</v>
       </c>
+      <c r="C7" t="n">
+        <v>3990.715885434302</v>
+      </c>
       <c r="D7" t="n">
         <v>1.77969e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>3610.714</v>
       </c>
+      <c r="C8" t="n">
+        <v>3937.608059513653</v>
+      </c>
       <c r="D8" t="n">
         <v>1.80211e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>3563.327</v>
       </c>
+      <c r="C9" t="n">
+        <v>3887.702905928389</v>
+      </c>
       <c r="D9" t="n">
         <v>1.82544e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>3515.496</v>
       </c>
+      <c r="C10" t="n">
+        <v>3838.126405014492</v>
+      </c>
       <c r="D10" t="n">
         <v>1.84556e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>3465.324</v>
       </c>
+      <c r="C11" t="n">
+        <v>3789.084040276995</v>
+      </c>
       <c r="D11" t="n">
         <v>1.86731e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>3416.541</v>
       </c>
+      <c r="C12" t="n">
+        <v>3742.219188785776</v>
+      </c>
       <c r="D12" t="n">
         <v>1.88939e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>3376.836</v>
       </c>
+      <c r="C13" t="n">
+        <v>3697.306124704689</v>
+      </c>
       <c r="D13" t="n">
         <v>1.90917e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>3334.832</v>
       </c>
+      <c r="C14" t="n">
+        <v>3656.861648217181</v>
+      </c>
       <c r="D14" t="n">
         <v>1.93086e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>3290.723</v>
       </c>
+      <c r="C15" t="n">
+        <v>3612.727569223353</v>
+      </c>
       <c r="D15" t="n">
         <v>1.95041e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>3250.783</v>
       </c>
+      <c r="C16" t="n">
+        <v>3574.825259750876</v>
+      </c>
       <c r="D16" t="n">
         <v>1.96802e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>3214.116</v>
       </c>
+      <c r="C17" t="n">
+        <v>3533.735248066606</v>
+      </c>
       <c r="D17" t="n">
         <v>1.98836e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>3173.643</v>
       </c>
+      <c r="C18" t="n">
+        <v>3495.717767894356</v>
+      </c>
       <c r="D18" t="n">
         <v>2.00852e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>3118.426</v>
       </c>
+      <c r="C19" t="n">
+        <v>3448.76879479597</v>
+      </c>
       <c r="D19" t="n">
         <v>2.02758e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>3093.033</v>
       </c>
+      <c r="C20" t="n">
+        <v>3415.535088558366</v>
+      </c>
       <c r="D20" t="n">
         <v>2.04808e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>3051.838</v>
       </c>
+      <c r="C21" t="n">
+        <v>3375.98213998792</v>
+      </c>
       <c r="D21" t="n">
         <v>2.06785e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>3016.932</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3338.076243926486</v>
       </c>
       <c r="D22" t="n">
         <v>2.08854e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>4238.991</v>
       </c>
+      <c r="C2" t="n">
+        <v>4555.206739763713</v>
+      </c>
       <c r="D2" t="n">
         <v>1.5612e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>4044.713</v>
       </c>
+      <c r="C3" t="n">
+        <v>4340.63501687285</v>
+      </c>
       <c r="D3" t="n">
         <v>1.6412e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>3976.748</v>
       </c>
+      <c r="C4" t="n">
+        <v>4275.787480917753</v>
+      </c>
       <c r="D4" t="n">
         <v>1.66899e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>3898.464</v>
       </c>
+      <c r="C5" t="n">
+        <v>4217.413203635683</v>
+      </c>
       <c r="D5" t="n">
         <v>1.6875e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>3854.403</v>
       </c>
+      <c r="C6" t="n">
+        <v>4168.049196292892</v>
+      </c>
       <c r="D6" t="n">
         <v>1.70957e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>3796.718</v>
       </c>
+      <c r="C7" t="n">
+        <v>4115.811572942816</v>
+      </c>
       <c r="D7" t="n">
         <v>1.72971e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>3744.883</v>
       </c>
+      <c r="C8" t="n">
+        <v>4061.302322287041</v>
+      </c>
       <c r="D8" t="n">
         <v>1.75369e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>3689.536</v>
       </c>
+      <c r="C9" t="n">
+        <v>4006.655108141874</v>
+      </c>
       <c r="D9" t="n">
         <v>1.7728e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>3638.875</v>
       </c>
+      <c r="C10" t="n">
+        <v>3952.477262617963</v>
+      </c>
       <c r="D10" t="n">
         <v>1.79443e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>3564.946</v>
       </c>
+      <c r="C11" t="n">
+        <v>3895.074036206186</v>
+      </c>
       <c r="D11" t="n">
         <v>1.8175e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>3535.694</v>
       </c>
+      <c r="C12" t="n">
+        <v>3852.278794572872</v>
+      </c>
       <c r="D12" t="n">
         <v>1.83656e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>3467.038</v>
       </c>
+      <c r="C13" t="n">
+        <v>3795.713754342875</v>
+      </c>
       <c r="D13" t="n">
         <v>1.85874e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>3445.639</v>
       </c>
+      <c r="C14" t="n">
+        <v>3759.501895682466</v>
+      </c>
       <c r="D14" t="n">
         <v>1.87932e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>3399.821</v>
       </c>
+      <c r="C15" t="n">
+        <v>3713.303220586056</v>
+      </c>
       <c r="D15" t="n">
         <v>1.89853e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>3340.591</v>
       </c>
+      <c r="C16" t="n">
+        <v>3666.444537711683</v>
+      </c>
       <c r="D16" t="n">
         <v>1.91801e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>3315.161</v>
       </c>
+      <c r="C17" t="n">
+        <v>3630.212590848703</v>
+      </c>
       <c r="D17" t="n">
         <v>1.93455e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>3277.023</v>
       </c>
+      <c r="C18" t="n">
+        <v>3590.400345750657</v>
+      </c>
       <c r="D18" t="n">
         <v>1.95506e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>3235.415</v>
       </c>
+      <c r="C19" t="n">
+        <v>3548.984298431118</v>
+      </c>
       <c r="D19" t="n">
         <v>1.97261e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>3178.289</v>
       </c>
+      <c r="C20" t="n">
+        <v>3503.330720578747</v>
+      </c>
       <c r="D20" t="n">
         <v>1.99104e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>3156.465</v>
       </c>
+      <c r="C21" t="n">
+        <v>3471.611282653759</v>
+      </c>
       <c r="D21" t="n">
         <v>2.0079e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>3101.983</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3427.942833334868</v>
       </c>
       <c r="D22" t="n">
         <v>2.02506e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>4912.635</v>
       </c>
+      <c r="C2" t="n">
+        <v>5249.732209477749</v>
+      </c>
       <c r="D2" t="n">
         <v>1.3433e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>4498.614</v>
       </c>
+      <c r="C3" t="n">
+        <v>4804.535225420356</v>
+      </c>
       <c r="D3" t="n">
         <v>1.48859e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>4393.312</v>
       </c>
+      <c r="C4" t="n">
+        <v>4694.864416878079</v>
+      </c>
       <c r="D4" t="n">
         <v>1.52935e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>4294.186</v>
       </c>
+      <c r="C5" t="n">
+        <v>4615.113830600692</v>
+      </c>
       <c r="D5" t="n">
         <v>1.55537e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>4235.998</v>
       </c>
+      <c r="C6" t="n">
+        <v>4555.602571717726</v>
+      </c>
       <c r="D6" t="n">
         <v>1.58011e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>4203.937</v>
       </c>
+      <c r="C7" t="n">
+        <v>4512.613696343234</v>
+      </c>
       <c r="D7" t="n">
         <v>1.59869e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>4128.549</v>
       </c>
+      <c r="C8" t="n">
+        <v>4454.869115540784</v>
+      </c>
       <c r="D8" t="n">
         <v>1.61974e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>4100.611</v>
       </c>
+      <c r="C9" t="n">
+        <v>4404.818051372833</v>
+      </c>
       <c r="D9" t="n">
         <v>1.63933e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>4037.859</v>
       </c>
+      <c r="C10" t="n">
+        <v>4343.543930376985</v>
+      </c>
       <c r="D10" t="n">
         <v>1.66272e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>3944.908</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4272.446612116149</v>
       </c>
       <c r="D11" t="n">
         <v>1.68759e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>4402.141</v>
       </c>
+      <c r="C2" t="n">
+        <v>4742.911195792382</v>
+      </c>
       <c r="D2" t="n">
         <v>1.52218e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>4176.882000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>4488.856183852946</v>
+      </c>
       <c r="D3" t="n">
         <v>1.60818e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>4089.772</v>
       </c>
+      <c r="C4" t="n">
+        <v>4401.522544350647</v>
+      </c>
       <c r="D4" t="n">
         <v>1.63931e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>4007.653</v>
       </c>
+      <c r="C5" t="n">
+        <v>4338.880556047943</v>
+      </c>
       <c r="D5" t="n">
         <v>1.66188e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>3963.018</v>
       </c>
+      <c r="C6" t="n">
+        <v>4292.663372178478</v>
+      </c>
       <c r="D6" t="n">
         <v>1.67974e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>3922.402</v>
       </c>
+      <c r="C7" t="n">
+        <v>4254.219198760435</v>
+      </c>
       <c r="D7" t="n">
         <v>1.69672e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>3890.286</v>
       </c>
+      <c r="C8" t="n">
+        <v>4221.740789050136</v>
+      </c>
       <c r="D8" t="n">
         <v>1.7081e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>3858.541</v>
       </c>
+      <c r="C9" t="n">
+        <v>4191.652515453288</v>
+      </c>
       <c r="D9" t="n">
         <v>1.72051e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>3812.463</v>
       </c>
+      <c r="C10" t="n">
+        <v>4141.695666737938</v>
+      </c>
       <c r="D10" t="n">
         <v>1.73961e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>3763.779</v>
       </c>
+      <c r="C11" t="n">
+        <v>4099.776448823087</v>
+      </c>
       <c r="D11" t="n">
         <v>1.75608e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>3730.284</v>
       </c>
+      <c r="C12" t="n">
+        <v>4066.272317614569</v>
+      </c>
       <c r="D12" t="n">
         <v>1.77166e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>3690.293</v>
       </c>
+      <c r="C13" t="n">
+        <v>4018.225543858666</v>
+      </c>
       <c r="D13" t="n">
         <v>1.79103e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>3645.16</v>
       </c>
+      <c r="C14" t="n">
+        <v>3972.975224127933</v>
+      </c>
       <c r="D14" t="n">
         <v>1.80806e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>3601.341</v>
       </c>
+      <c r="C15" t="n">
+        <v>3940.189726342663</v>
+      </c>
       <c r="D15" t="n">
         <v>1.82497e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>3569.599</v>
       </c>
+      <c r="C16" t="n">
+        <v>3900.62186051976</v>
+      </c>
       <c r="D16" t="n">
         <v>1.84262e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>3526.349</v>
       </c>
+      <c r="C17" t="n">
+        <v>3858.346951867173</v>
+      </c>
       <c r="D17" t="n">
         <v>1.86058e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>3485.29</v>
       </c>
+      <c r="C18" t="n">
+        <v>3814.785485002801</v>
+      </c>
       <c r="D18" t="n">
         <v>1.87802e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>3424.659</v>
       </c>
+      <c r="C19" t="n">
+        <v>3770.693187163068</v>
+      </c>
       <c r="D19" t="n">
         <v>1.89428e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>3407.722</v>
       </c>
+      <c r="C20" t="n">
+        <v>3740.818133126701</v>
+      </c>
       <c r="D20" t="n">
         <v>1.91044e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>3350.828</v>
       </c>
+      <c r="C21" t="n">
+        <v>3696.006652664463</v>
+      </c>
       <c r="D21" t="n">
         <v>1.92914e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>3324.337</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3658.638213383156</v>
       </c>
       <c r="D22" t="n">
         <v>1.94327e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>5171.343</v>
       </c>
+      <c r="C2" t="n">
+        <v>5574.912123415053</v>
+      </c>
       <c r="D2" t="n">
         <v>1.25118e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>4432.228</v>
       </c>
+      <c r="C3" t="n">
+        <v>4763.316159328083</v>
+      </c>
       <c r="D3" t="n">
         <v>1.48536e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>4246.938</v>
       </c>
+      <c r="C4" t="n">
+        <v>4574.815254730323</v>
+      </c>
       <c r="D4" t="n">
         <v>1.55454e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>4145.025000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>4482.166217714448</v>
+      </c>
       <c r="D5" t="n">
         <v>1.58499e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>4097.360000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>4422.820774889178</v>
+      </c>
       <c r="D6" t="n">
         <v>1.61178e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>4014.645</v>
       </c>
+      <c r="C7" t="n">
+        <v>4356.337983501533</v>
+      </c>
       <c r="D7" t="n">
         <v>1.63544e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>3958.379</v>
       </c>
+      <c r="C8" t="n">
+        <v>4303.411901900567</v>
+      </c>
       <c r="D8" t="n">
         <v>1.65559e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>3895.914</v>
       </c>
+      <c r="C9" t="n">
+        <v>4247.567658844417</v>
+      </c>
       <c r="D9" t="n">
         <v>1.677e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>3844.036</v>
       </c>
+      <c r="C10" t="n">
+        <v>4190.498029460265</v>
+      </c>
       <c r="D10" t="n">
         <v>1.69951e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>3793.37</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4141.190741514576</v>
       </c>
       <c r="D11" t="n">
         <v>1.72019e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>4136.258000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>4482.487995456688</v>
+      </c>
       <c r="D2" t="n">
         <v>1.59485e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>3952.457</v>
       </c>
+      <c r="C3" t="n">
+        <v>4281.049828663809</v>
+      </c>
       <c r="D3" t="n">
         <v>1.6696e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>3882.862</v>
       </c>
+      <c r="C4" t="n">
+        <v>4206.779652213148</v>
+      </c>
       <c r="D4" t="n">
         <v>1.68079e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>3833.271999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>4164.182615171735</v>
+      </c>
       <c r="D5" t="n">
         <v>1.70118e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>3787.416999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>4119.023947544148</v>
+      </c>
       <c r="D6" t="n">
         <v>1.71893e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>3747.302</v>
       </c>
+      <c r="C7" t="n">
+        <v>4073.799750050469</v>
+      </c>
       <c r="D7" t="n">
         <v>1.73724e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>3699.331</v>
       </c>
+      <c r="C8" t="n">
+        <v>4030.908855449173</v>
+      </c>
       <c r="D8" t="n">
         <v>1.75619e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>3657.599</v>
       </c>
+      <c r="C9" t="n">
+        <v>3988.035422692396</v>
+      </c>
       <c r="D9" t="n">
         <v>1.7739e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>3622.848</v>
       </c>
+      <c r="C10" t="n">
+        <v>3954.551676450738</v>
+      </c>
       <c r="D10" t="n">
         <v>1.78938e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>3583.788</v>
       </c>
+      <c r="C11" t="n">
+        <v>3915.24934647971</v>
+      </c>
       <c r="D11" t="n">
         <v>1.80722e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>3543.513</v>
       </c>
+      <c r="C12" t="n">
+        <v>3876.053059089986</v>
+      </c>
       <c r="D12" t="n">
         <v>1.8242e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>3487.706</v>
       </c>
+      <c r="C13" t="n">
+        <v>3831.430229637688</v>
+      </c>
       <c r="D13" t="n">
         <v>1.8382e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>3474.855</v>
       </c>
+      <c r="C14" t="n">
+        <v>3807.830676038274</v>
+      </c>
       <c r="D14" t="n">
         <v>1.8567e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>3443.096</v>
       </c>
+      <c r="C15" t="n">
+        <v>3769.417598548494</v>
+      </c>
       <c r="D15" t="n">
         <v>1.87101e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>3404.245</v>
       </c>
+      <c r="C16" t="n">
+        <v>3731.700633865903</v>
+      </c>
       <c r="D16" t="n">
         <v>1.88897e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>3373.864</v>
       </c>
+      <c r="C17" t="n">
+        <v>3700.679683437095</v>
+      </c>
       <c r="D17" t="n">
         <v>1.90441e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>3334.496</v>
       </c>
+      <c r="C18" t="n">
+        <v>3663.987226290485</v>
+      </c>
       <c r="D18" t="n">
         <v>1.92083e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>3301.107</v>
       </c>
+      <c r="C19" t="n">
+        <v>3627.848680302762</v>
+      </c>
       <c r="D19" t="n">
         <v>1.93752e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>3242.685</v>
       </c>
+      <c r="C20" t="n">
+        <v>3581.978223539385</v>
+      </c>
       <c r="D20" t="n">
         <v>1.95656e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>3205.215</v>
       </c>
+      <c r="C21" t="n">
+        <v>3540.94067960953</v>
+      </c>
       <c r="D21" t="n">
         <v>1.97413e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>3186.589</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3510.831799213346</v>
       </c>
       <c r="D22" t="n">
         <v>1.99301e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>4348.036</v>
       </c>
+      <c r="C2" t="n">
+        <v>4700.280106175786</v>
+      </c>
       <c r="D2" t="n">
         <v>1.51106e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>3940.101000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>4272.403213518042</v>
+      </c>
       <c r="D3" t="n">
         <v>1.66723e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>3843.614</v>
       </c>
+      <c r="C4" t="n">
+        <v>4170.434219421229</v>
+      </c>
       <c r="D4" t="n">
         <v>1.71e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>3780.592</v>
       </c>
+      <c r="C5" t="n">
+        <v>4112.35277809266</v>
+      </c>
       <c r="D5" t="n">
         <v>1.73286e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>3728.027</v>
       </c>
+      <c r="C6" t="n">
+        <v>4057.232453020977</v>
+      </c>
       <c r="D6" t="n">
         <v>1.75587e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>3675.832</v>
       </c>
+      <c r="C7" t="n">
+        <v>4004.464255156422</v>
+      </c>
       <c r="D7" t="n">
         <v>1.77914e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>3616.231</v>
       </c>
+      <c r="C8" t="n">
+        <v>3948.310602164721</v>
+      </c>
       <c r="D8" t="n">
         <v>1.80104e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>3558.578</v>
       </c>
+      <c r="C9" t="n">
+        <v>3893.523923085867</v>
+      </c>
       <c r="D9" t="n">
         <v>1.82413e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>3509.456</v>
       </c>
+      <c r="C10" t="n">
+        <v>3842.582873168538</v>
+      </c>
       <c r="D10" t="n">
         <v>1.84824e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>3436.622</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3786.307367924245</v>
       </c>
       <c r="D11" t="n">
         <v>1.87218e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>4125.245</v>
       </c>
+      <c r="C2" t="n">
+        <v>4483.163801408125</v>
+      </c>
       <c r="D2" t="n">
         <v>1.60268e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>3945.581000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>4259.132188697948</v>
+      </c>
       <c r="D3" t="n">
         <v>1.68472e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>3854.231</v>
       </c>
+      <c r="C4" t="n">
+        <v>4183.069836279103</v>
+      </c>
       <c r="D4" t="n">
         <v>1.7086e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>3798.029</v>
       </c>
+      <c r="C5" t="n">
+        <v>4128.305020271271</v>
+      </c>
       <c r="D5" t="n">
         <v>1.72934e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>3745.503</v>
       </c>
+      <c r="C6" t="n">
+        <v>4081.255735069864</v>
+      </c>
       <c r="D6" t="n">
         <v>1.75009e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>3701.435</v>
       </c>
+      <c r="C7" t="n">
+        <v>4034.318880028927</v>
+      </c>
       <c r="D7" t="n">
         <v>1.76893e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>3654.411</v>
       </c>
+      <c r="C8" t="n">
+        <v>3986.167668749661</v>
+      </c>
       <c r="D8" t="n">
         <v>1.78711e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>3604.128</v>
       </c>
+      <c r="C9" t="n">
+        <v>3938.47345351722</v>
+      </c>
       <c r="D9" t="n">
         <v>1.81076e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>3557.757</v>
       </c>
+      <c r="C10" t="n">
+        <v>3888.941179975794</v>
+      </c>
       <c r="D10" t="n">
         <v>1.83017e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>3514.675</v>
       </c>
+      <c r="C11" t="n">
+        <v>3847.390231754518</v>
+      </c>
       <c r="D11" t="n">
         <v>1.85024e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>3459.314</v>
       </c>
+      <c r="C12" t="n">
+        <v>3802.548247462247</v>
+      </c>
       <c r="D12" t="n">
         <v>1.86781e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>3436.244</v>
       </c>
+      <c r="C13" t="n">
+        <v>3762.847249333924</v>
+      </c>
       <c r="D13" t="n">
         <v>1.88562e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>3399.643</v>
       </c>
+      <c r="C14" t="n">
+        <v>3731.557428663083</v>
+      </c>
       <c r="D14" t="n">
         <v>1.90275e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>3363.146</v>
       </c>
+      <c r="C15" t="n">
+        <v>3692.590646104326</v>
+      </c>
       <c r="D15" t="n">
         <v>1.9224e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>3323.491</v>
       </c>
+      <c r="C16" t="n">
+        <v>3656.200500423397</v>
+      </c>
       <c r="D16" t="n">
         <v>1.93855e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>3280.727</v>
       </c>
+      <c r="C17" t="n">
+        <v>3611.300891899984</v>
+      </c>
       <c r="D17" t="n">
         <v>1.95844e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>3230.648</v>
       </c>
+      <c r="C18" t="n">
+        <v>3568.325696749039</v>
+      </c>
       <c r="D18" t="n">
         <v>1.975e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>3191.834</v>
       </c>
+      <c r="C19" t="n">
+        <v>3530.528851892328</v>
+      </c>
       <c r="D19" t="n">
         <v>1.99353e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>3153.2</v>
       </c>
+      <c r="C20" t="n">
+        <v>3491.668940095174</v>
+      </c>
       <c r="D20" t="n">
         <v>2.01235e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>3116.067</v>
       </c>
+      <c r="C21" t="n">
+        <v>3456.225967248421</v>
+      </c>
       <c r="D21" t="n">
         <v>2.03047e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>3083.189</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3418.46550043226</v>
       </c>
       <c r="D22" t="n">
         <v>2.04658e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>2712.444</v>
       </c>
+      <c r="C2" t="n">
+        <v>3090.249317850884</v>
+      </c>
       <c r="D2" t="n">
         <v>2.16796e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>2677.859</v>
       </c>
+      <c r="C3" t="n">
+        <v>3075.190504058026</v>
+      </c>
       <c r="D3" t="n">
         <v>2.18813e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>2644.616</v>
       </c>
+      <c r="C4" t="n">
+        <v>3035.331626809811</v>
+      </c>
       <c r="D4" t="n">
         <v>2.21057e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>2589.299</v>
       </c>
+      <c r="C5" t="n">
+        <v>2989.662409218816</v>
+      </c>
       <c r="D5" t="n">
         <v>2.2363e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>2510.877</v>
       </c>
+      <c r="C6" t="n">
+        <v>2911.944225855837</v>
+      </c>
       <c r="D6" t="n">
         <v>2.27372e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>2447.341</v>
       </c>
+      <c r="C7" t="n">
+        <v>2856.221631062224</v>
+      </c>
       <c r="D7" t="n">
         <v>2.30685e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>2386.682</v>
       </c>
+      <c r="C8" t="n">
+        <v>2796.704582437426</v>
+      </c>
       <c r="D8" t="n">
         <v>2.34173e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>2304.896</v>
       </c>
+      <c r="C9" t="n">
+        <v>2724.179088907667</v>
+      </c>
       <c r="D9" t="n">
         <v>2.38033e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>2244.728</v>
       </c>
+      <c r="C10" t="n">
+        <v>2657.804984220966</v>
+      </c>
       <c r="D10" t="n">
         <v>2.41739e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>2171.918</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2588.76261300549</v>
       </c>
       <c r="D11" t="n">
         <v>2.44954e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 59.xlsx
@@ -565,7 +565,7 @@
         <v>4410.893</v>
       </c>
       <c r="C2" t="n">
-        <v>4725.49282168417</v>
+        <v>14760.34333618508</v>
       </c>
       <c r="D2" t="n">
         <v>1.49611e-07</v>
@@ -598,10 +598,7 @@
         <v>-34949.74027125462</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.322490181638291e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5583.107734286695</v>
+        <v>-9285.164659519451</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000005e-08</v>
@@ -618,7 +615,7 @@
         <v>4194.489</v>
       </c>
       <c r="C3" t="n">
-        <v>4519.87531865947</v>
+        <v>15405.43911544458</v>
       </c>
       <c r="D3" t="n">
         <v>1.56976e-07</v>
@@ -651,10 +648,7 @@
         <v>-34247.62471243175</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08515318850282e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5386.849633954452</v>
+        <v>-10177.54724192219</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000017e-08</v>
@@ -671,7 +665,7 @@
         <v>4157.799</v>
       </c>
       <c r="C4" t="n">
-        <v>4459.037660286593</v>
+        <v>15815.62266248669</v>
       </c>
       <c r="D4" t="n">
         <v>1.59836e-07</v>
@@ -704,10 +698,7 @@
         <v>-38595.47728812735</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.216578086636515e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5304.605237462032</v>
+        <v>-10682.22942151847</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000373e-08</v>
@@ -724,7 +715,7 @@
         <v>4100.618</v>
       </c>
       <c r="C5" t="n">
-        <v>4403.495716325665</v>
+        <v>15401.38461951595</v>
       </c>
       <c r="D5" t="n">
         <v>1.6234e-07</v>
@@ -757,10 +748,7 @@
         <v>-39672.8282293405</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.524288877266776e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5230.242124471747</v>
+        <v>-10333.54627776978</v>
       </c>
       <c r="AA5" t="n">
         <v>1.0000000000002e-08</v>
@@ -777,7 +765,7 @@
         <v>4025.463</v>
       </c>
       <c r="C6" t="n">
-        <v>4331.451187400209</v>
+        <v>15766.67148105929</v>
       </c>
       <c r="D6" t="n">
         <v>1.65025e-07</v>
@@ -810,10 +798,7 @@
         <v>-39709.58658496476</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.028636438670053e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5142.944730989095</v>
+        <v>-10787.855952499</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000073e-08</v>
@@ -830,7 +815,7 @@
         <v>3964.407</v>
       </c>
       <c r="C7" t="n">
-        <v>4267.933394411134</v>
+        <v>15596.40000373145</v>
       </c>
       <c r="D7" t="n">
         <v>1.67483e-07</v>
@@ -863,10 +848,7 @@
         <v>-40150.35943430225</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.708709045667614e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5063.695151031015</v>
+        <v>-10686.03195260783</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000002e-08</v>
@@ -883,7 +865,7 @@
         <v>3877.833</v>
       </c>
       <c r="C8" t="n">
-        <v>4197.500593028707</v>
+        <v>15884.81928497305</v>
       </c>
       <c r="D8" t="n">
         <v>1.69992e-07</v>
@@ -916,10 +898,7 @@
         <v>-36995.66520938126</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.425339802973112e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4987.932255327967</v>
+        <v>-11051.82899921041</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000079e-08</v>
@@ -936,7 +915,7 @@
         <v>3817.962</v>
       </c>
       <c r="C9" t="n">
-        <v>4142.219813032094</v>
+        <v>15809.78198510709</v>
       </c>
       <c r="D9" t="n">
         <v>1.72076e-07</v>
@@ -969,10 +948,7 @@
         <v>-36805.81640445982</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.097209174254449e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4916.332228474741</v>
+        <v>-11035.74470104395</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000002425e-08</v>
@@ -989,7 +965,7 @@
         <v>3767.345</v>
       </c>
       <c r="C10" t="n">
-        <v>4084.731711900554</v>
+        <v>15604.82585462592</v>
       </c>
       <c r="D10" t="n">
         <v>1.74308e-07</v>
@@ -1022,10 +998,7 @@
         <v>-37054.32768026136</v>
       </c>
       <c r="Y10" t="n">
-        <v>652.3999456314157</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7507.460051448403</v>
+        <v>-10889.676085716</v>
       </c>
       <c r="AA10" t="n">
         <v>7.729412589657326e-08</v>
@@ -1042,7 +1015,7 @@
         <v>3714.126</v>
       </c>
       <c r="C11" t="n">
-        <v>4034.098724752016</v>
+        <v>15329.59649353611</v>
       </c>
       <c r="D11" t="n">
         <v>1.76688e-07</v>
@@ -1075,10 +1048,7 @@
         <v>-37406.30490186359</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.662142564047953e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4783.521996762501</v>
+        <v>-10672.56103251811</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000002e-08</v>
@@ -1241,7 +1211,7 @@
         <v>4076.877</v>
       </c>
       <c r="C2" t="n">
-        <v>4393.72395749659</v>
+        <v>15217.06672993445</v>
       </c>
       <c r="D2" t="n">
         <v>1.62054e-07</v>
@@ -1274,10 +1244,7 @@
         <v>-35638.01056827818</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.041712370402108e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5190.418689250138</v>
+        <v>-10169.54327302346</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000001e-08</v>
@@ -1294,7 +1261,7 @@
         <v>3884.529</v>
       </c>
       <c r="C3" t="n">
-        <v>4209.792337047694</v>
+        <v>15844.02412901389</v>
       </c>
       <c r="D3" t="n">
         <v>1.68724e-07</v>
@@ -1327,10 +1294,7 @@
         <v>-33841.96714582125</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.282798808123782e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5007.551366894228</v>
+        <v>-10998.40527511918</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000088e-08</v>
@@ -1347,7 +1311,7 @@
         <v>3820.036</v>
       </c>
       <c r="C4" t="n">
-        <v>4143.996829012391</v>
+        <v>15463.47976076748</v>
       </c>
       <c r="D4" t="n">
         <v>1.71526e-07</v>
@@ -1380,10 +1344,7 @@
         <v>-34389.50879715473</v>
       </c>
       <c r="Y4" t="n">
-        <v>664.577608704921</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7616.150121410304</v>
+        <v>-10686.15711893401</v>
       </c>
       <c r="AA4" t="n">
         <v>7.465314260754322e-08</v>
@@ -1400,7 +1361,7 @@
         <v>3792.666</v>
       </c>
       <c r="C5" t="n">
-        <v>4104.83708909647</v>
+        <v>15483.92433009631</v>
       </c>
       <c r="D5" t="n">
         <v>1.73552e-07</v>
@@ -1433,10 +1394,7 @@
         <v>-37435.23747050085</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.915408073978983e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4868.791522028605</v>
+        <v>-10763.9954647084</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000915e-08</v>
@@ -1453,7 +1411,7 @@
         <v>3713.832</v>
       </c>
       <c r="C6" t="n">
-        <v>4039.035751822627</v>
+        <v>15387.54383814102</v>
       </c>
       <c r="D6" t="n">
         <v>1.75917e-07</v>
@@ -1486,10 +1444,7 @@
         <v>-35290.50595546336</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.313112773867714e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4804.054973645768</v>
+        <v>-10728.54098573031</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000079e-08</v>
@@ -1506,7 +1461,7 @@
         <v>3663.06</v>
       </c>
       <c r="C7" t="n">
-        <v>3990.715885434302</v>
+        <v>15832.17992082619</v>
       </c>
       <c r="D7" t="n">
         <v>1.77969e-07</v>
@@ -1539,10 +1494,7 @@
         <v>-35402.63585442989</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.042814161225317e-18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4739.387227142071</v>
+        <v>-11236.29069752135</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -1559,7 +1511,7 @@
         <v>3610.714</v>
       </c>
       <c r="C8" t="n">
-        <v>3937.608059513653</v>
+        <v>15673.58302252468</v>
       </c>
       <c r="D8" t="n">
         <v>1.80211e-07</v>
@@ -1592,10 +1544,7 @@
         <v>-35428.55066459881</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.882918239440259e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4672.725282587521</v>
+        <v>-11133.18545690676</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000002507e-08</v>
@@ -1612,7 +1561,7 @@
         <v>3563.327</v>
       </c>
       <c r="C9" t="n">
-        <v>3887.702905928389</v>
+        <v>15705.56120121652</v>
       </c>
       <c r="D9" t="n">
         <v>1.82544e-07</v>
@@ -1645,10 +1594,7 @@
         <v>-36175.26903805372</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.785911820519718e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4609.564847509468</v>
+        <v>-11225.33295345194</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001052e-08</v>
@@ -1665,7 +1611,7 @@
         <v>3515.496</v>
       </c>
       <c r="C10" t="n">
-        <v>3838.126405014492</v>
+        <v>15420.15585692361</v>
       </c>
       <c r="D10" t="n">
         <v>1.84556e-07</v>
@@ -1698,10 +1644,7 @@
         <v>-35522.52828418079</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.512958789529411e-14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4548.653427379078</v>
+        <v>-10987.12868690486</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1718,7 +1661,7 @@
         <v>3465.324</v>
       </c>
       <c r="C11" t="n">
-        <v>3789.084040276995</v>
+        <v>15826.38676301391</v>
       </c>
       <c r="D11" t="n">
         <v>1.86731e-07</v>
@@ -1751,10 +1694,7 @@
         <v>-35721.38862807961</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.021074950856468e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4484.324940651881</v>
+        <v>-11456.16893234202</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000371e-08</v>
@@ -1771,7 +1711,7 @@
         <v>3416.541</v>
       </c>
       <c r="C12" t="n">
-        <v>3742.219188785776</v>
+        <v>15538.43385449105</v>
       </c>
       <c r="D12" t="n">
         <v>1.88939e-07</v>
@@ -1804,10 +1744,7 @@
         <v>-36072.53079493461</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.188498569151061e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4424.978989228639</v>
+        <v>-11217.76827662383</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000003e-08</v>
@@ -1824,7 +1761,7 @@
         <v>3376.836</v>
       </c>
       <c r="C13" t="n">
-        <v>3697.306124704689</v>
+        <v>15740.18605106924</v>
       </c>
       <c r="D13" t="n">
         <v>1.90917e-07</v>
@@ -1857,10 +1794,7 @@
         <v>-36233.45634573063</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.254785065452177e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4369.449685422155</v>
+        <v>-11471.6453014835</v>
       </c>
       <c r="AA13" t="n">
         <v>1.00000000000007e-08</v>
@@ -1877,7 +1811,7 @@
         <v>3334.832</v>
       </c>
       <c r="C14" t="n">
-        <v>3656.861648217181</v>
+        <v>15885.71954969261</v>
       </c>
       <c r="D14" t="n">
         <v>1.93086e-07</v>
@@ -1910,10 +1844,7 @@
         <v>-36370.50788163688</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.309381043340392e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4315.36498574599</v>
+        <v>-11670.94038638662</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000065e-08</v>
@@ -1930,7 +1861,7 @@
         <v>3290.723</v>
       </c>
       <c r="C15" t="n">
-        <v>3612.727569223353</v>
+        <v>15824.59903320175</v>
       </c>
       <c r="D15" t="n">
         <v>1.95041e-07</v>
@@ -1963,10 +1894,7 @@
         <v>-36607.14753669461</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.498589118958575e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4262.919131796325</v>
+        <v>-11656.04896752604</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000004e-08</v>
@@ -1983,7 +1911,7 @@
         <v>3250.783</v>
       </c>
       <c r="C16" t="n">
-        <v>3574.825259750876</v>
+        <v>16071.77018247415</v>
       </c>
       <c r="D16" t="n">
         <v>1.96802e-07</v>
@@ -2016,10 +1944,7 @@
         <v>-36528.55938395589</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.024938271445678e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4212.695729862809</v>
+        <v>-11950.37725272443</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000004813e-08</v>
@@ -2036,7 +1961,7 @@
         <v>3214.116</v>
       </c>
       <c r="C17" t="n">
-        <v>3533.735248066606</v>
+        <v>16061.02199238965</v>
       </c>
       <c r="D17" t="n">
         <v>1.98836e-07</v>
@@ -2069,10 +1994,7 @@
         <v>-36972.1037326141</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.191183304021579e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4162.294867322231</v>
+        <v>-11986.51010327217</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000003e-08</v>
@@ -2089,7 +2011,7 @@
         <v>3173.643</v>
       </c>
       <c r="C18" t="n">
-        <v>3495.717767894356</v>
+        <v>16260.52495195264</v>
       </c>
       <c r="D18" t="n">
         <v>2.00852e-07</v>
@@ -2122,10 +2044,7 @@
         <v>-37168.63427339826</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.418482124898383e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4111.877337241065</v>
+        <v>-12235.84542822116</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000000001e-08</v>
@@ -2142,7 +2061,7 @@
         <v>3118.426</v>
       </c>
       <c r="C19" t="n">
-        <v>3448.76879479597</v>
+        <v>16113.17046208878</v>
       </c>
       <c r="D19" t="n">
         <v>2.02758e-07</v>
@@ -2175,10 +2094,7 @@
         <v>-34304.69247457368</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.024354633209548e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4060.130789794031</v>
+        <v>-12130.97009454394</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000012e-08</v>
@@ -2195,7 +2111,7 @@
         <v>3093.033</v>
       </c>
       <c r="C20" t="n">
-        <v>3415.535088558366</v>
+        <v>16411.82531669121</v>
       </c>
       <c r="D20" t="n">
         <v>2.04808e-07</v>
@@ -2228,10 +2144,7 @@
         <v>-37301.53965250017</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.766698240717566e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4010.225018695057</v>
+        <v>-12480.66591367425</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000009e-08</v>
@@ -2248,7 +2161,7 @@
         <v>3051.838</v>
       </c>
       <c r="C21" t="n">
-        <v>3375.98213998792</v>
+        <v>16256.96376346135</v>
       </c>
       <c r="D21" t="n">
         <v>2.06785e-07</v>
@@ -2281,10 +2194,7 @@
         <v>-37154.5760904905</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.042463000883891e-13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3959.688198823024</v>
+        <v>-12368.152315586</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -2301,7 +2211,7 @@
         <v>3016.932</v>
       </c>
       <c r="C22" t="n">
-        <v>3338.076243926486</v>
+        <v>15635.4474638157</v>
       </c>
       <c r="D22" t="n">
         <v>2.08854e-07</v>
@@ -2334,10 +2244,7 @@
         <v>-37672.84918226556</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.477213977656566e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3910.339024993793</v>
+        <v>-11782.04859973442</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000343e-08</v>
@@ -2500,7 +2407,7 @@
         <v>4238.991</v>
       </c>
       <c r="C2" t="n">
-        <v>4555.206739763713</v>
+        <v>14617.7787331991</v>
       </c>
       <c r="D2" t="n">
         <v>1.5612e-07</v>
@@ -2533,10 +2440,7 @@
         <v>-35506.15553823351</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.12796442330429e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5366.106587401639</v>
+        <v>-9361.286180126861</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000091e-08</v>
@@ -2553,7 +2457,7 @@
         <v>4044.713</v>
       </c>
       <c r="C3" t="n">
-        <v>4340.63501687285</v>
+        <v>14936.9867095524</v>
       </c>
       <c r="D3" t="n">
         <v>1.6412e-07</v>
@@ -2586,10 +2490,7 @@
         <v>-37843.31046919891</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.358630500636043e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5154.893764619088</v>
+        <v>-9922.776162789451</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000021e-08</v>
@@ -2606,7 +2507,7 @@
         <v>3976.748</v>
       </c>
       <c r="C4" t="n">
-        <v>4275.787480917753</v>
+        <v>14798.55509726134</v>
       </c>
       <c r="D4" t="n">
         <v>1.66899e-07</v>
@@ -2639,10 +2540,7 @@
         <v>-38703.55550281583</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.33898490965731e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5079.133315690301</v>
+        <v>-9860.03499551861</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000019748e-08</v>
@@ -2659,7 +2557,7 @@
         <v>3898.464</v>
       </c>
       <c r="C5" t="n">
-        <v>4217.413203635683</v>
+        <v>15459.47979467029</v>
       </c>
       <c r="D5" t="n">
         <v>1.6875e-07</v>
@@ -2692,10 +2590,7 @@
         <v>-35519.92350740529</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.871717218986488e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5016.833931319816</v>
+        <v>-10587.39190041121</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000473e-08</v>
@@ -2712,7 +2607,7 @@
         <v>3854.403</v>
       </c>
       <c r="C6" t="n">
-        <v>4168.049196292892</v>
+        <v>15369.37794293167</v>
       </c>
       <c r="D6" t="n">
         <v>1.70957e-07</v>
@@ -2745,10 +2640,7 @@
         <v>-36190.53986210329</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.093700857085619e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4954.367840392837</v>
+        <v>-10556.31716394909</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003275e-08</v>
@@ -2765,7 +2657,7 @@
         <v>3796.718</v>
       </c>
       <c r="C7" t="n">
-        <v>4115.811572942816</v>
+        <v>15306.85097059438</v>
       </c>
       <c r="D7" t="n">
         <v>1.72971e-07</v>
@@ -2798,10 +2690,7 @@
         <v>-36524.15846274816</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.99309243042633e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4887.203761068454</v>
+        <v>-10550.39419642572</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000115e-08</v>
@@ -2818,7 +2707,7 @@
         <v>3744.883</v>
       </c>
       <c r="C8" t="n">
-        <v>4061.302322287041</v>
+        <v>15167.86238349012</v>
       </c>
       <c r="D8" t="n">
         <v>1.75369e-07</v>
@@ -2851,10 +2740,7 @@
         <v>-36822.25767527945</v>
       </c>
       <c r="Y8" t="n">
-        <v>650.5487553003969</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7497.600182374447</v>
+        <v>-10472.9256909314</v>
       </c>
       <c r="AA8" t="n">
         <v>7.896013854493883e-08</v>
@@ -2871,7 +2757,7 @@
         <v>3689.536</v>
       </c>
       <c r="C9" t="n">
-        <v>4006.655108141874</v>
+        <v>15144.31664166876</v>
       </c>
       <c r="D9" t="n">
         <v>1.7728e-07</v>
@@ -2904,10 +2790,7 @@
         <v>-36337.10509617209</v>
       </c>
       <c r="Y9" t="n">
-        <v>184.2010763089851</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5533.965751206717</v>
+        <v>-10504.69277382792</v>
       </c>
       <c r="AA9" t="n">
         <v>1.582626604446298e-08</v>
@@ -2924,7 +2807,7 @@
         <v>3638.875</v>
       </c>
       <c r="C10" t="n">
-        <v>3952.477262617963</v>
+        <v>15419.08188604075</v>
       </c>
       <c r="D10" t="n">
         <v>1.79443e-07</v>
@@ -2957,10 +2840,7 @@
         <v>-36714.10591701655</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.567484888076167e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4685.989113430082</v>
+        <v>-10843.53688655552</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000092e-08</v>
@@ -2977,7 +2857,7 @@
         <v>3564.946</v>
       </c>
       <c r="C11" t="n">
-        <v>3895.074036206186</v>
+        <v>15822.95359560404</v>
       </c>
       <c r="D11" t="n">
         <v>1.8175e-07</v>
@@ -3010,10 +2890,7 @@
         <v>-33994.71803217534</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.794987213779631e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4621.200738719145</v>
+        <v>-11315.05672214541</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004072e-08</v>
@@ -3030,7 +2907,7 @@
         <v>3535.694</v>
       </c>
       <c r="C12" t="n">
-        <v>3852.278794572872</v>
+        <v>16069.67676210459</v>
       </c>
       <c r="D12" t="n">
         <v>1.83656e-07</v>
@@ -3063,10 +2940,7 @@
         <v>-37175.1195296579</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.828000112801305e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4558.900484609763</v>
+        <v>-11619.22538123562</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000346e-08</v>
@@ -3083,7 +2957,7 @@
         <v>3467.038</v>
       </c>
       <c r="C13" t="n">
-        <v>3795.713754342875</v>
+        <v>15331.01209030932</v>
       </c>
       <c r="D13" t="n">
         <v>1.85874e-07</v>
@@ -3116,10 +2990,7 @@
         <v>-34276.11164957892</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.572115893842794e-13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4497.35942103051</v>
+        <v>-10924.53122374246</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000159e-08</v>
@@ -3136,7 +3007,7 @@
         <v>3445.639</v>
       </c>
       <c r="C14" t="n">
-        <v>3759.501895682466</v>
+        <v>15411.48768153942</v>
       </c>
       <c r="D14" t="n">
         <v>1.87932e-07</v>
@@ -3169,10 +3040,7 @@
         <v>-37789.89943438322</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.479636554324082e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4439.712303933526</v>
+        <v>-11058.90626176556</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000042e-08</v>
@@ -3189,7 +3057,7 @@
         <v>3399.821</v>
       </c>
       <c r="C15" t="n">
-        <v>3713.303220586056</v>
+        <v>16096.17582912674</v>
       </c>
       <c r="D15" t="n">
         <v>1.89853e-07</v>
@@ -3222,10 +3090,7 @@
         <v>-37870.03227907918</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.375642885466738e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4383.329264891176</v>
+        <v>-11805.97551087856</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000005306e-08</v>
@@ -3242,7 +3107,7 @@
         <v>3340.591</v>
       </c>
       <c r="C16" t="n">
-        <v>3666.444537711683</v>
+        <v>16156.17674823795</v>
       </c>
       <c r="D16" t="n">
         <v>1.91801e-07</v>
@@ -3275,10 +3140,7 @@
         <v>-34652.04904895611</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.404954652065036e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4330.319985182471</v>
+        <v>-11916.45437453819</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000004e-08</v>
@@ -3295,7 +3157,7 @@
         <v>3315.161</v>
       </c>
       <c r="C17" t="n">
-        <v>3630.212590848703</v>
+        <v>16010.36031366238</v>
       </c>
       <c r="D17" t="n">
         <v>1.93455e-07</v>
@@ -3328,10 +3190,7 @@
         <v>-37780.09590416515</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.805415153796025e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4277.167962881332</v>
+        <v>-11811.69980700786</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000001209e-08</v>
@@ -3348,7 +3207,7 @@
         <v>3277.023</v>
       </c>
       <c r="C18" t="n">
-        <v>3590.400345750657</v>
+        <v>15510.23065048477</v>
       </c>
       <c r="D18" t="n">
         <v>1.95506e-07</v>
@@ -3381,10 +3240,7 @@
         <v>-38311.15347739121</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.816701101113977e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4225.68020968566</v>
+        <v>-11351.87366905576</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000236e-08</v>
@@ -3401,7 +3257,7 @@
         <v>3235.415</v>
       </c>
       <c r="C19" t="n">
-        <v>3548.984298431118</v>
+        <v>16123.70161043485</v>
       </c>
       <c r="D19" t="n">
         <v>1.97261e-07</v>
@@ -3434,10 +3290,7 @@
         <v>-38188.80215856789</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.585499830558922e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4173.986103237598</v>
+        <v>-12020.96611370494</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000023e-08</v>
@@ -3454,7 +3307,7 @@
         <v>3178.289</v>
       </c>
       <c r="C20" t="n">
-        <v>3503.330720578747</v>
+        <v>16158.96211068886</v>
       </c>
       <c r="D20" t="n">
         <v>1.99104e-07</v>
@@ -3487,10 +3340,7 @@
         <v>-34785.64355131798</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.676181817938063e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4125.638854984247</v>
+        <v>-12101.46998328359</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000074e-08</v>
@@ -3507,7 +3357,7 @@
         <v>3156.465</v>
       </c>
       <c r="C21" t="n">
-        <v>3471.611282653759</v>
+        <v>16165.52730960206</v>
       </c>
       <c r="D21" t="n">
         <v>2.0079e-07</v>
@@ -3540,10 +3390,7 @@
         <v>-37980.33859770725</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.086950797531119e-11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4076.108843503315</v>
+        <v>-12151.08891917656</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000079e-08</v>
@@ -3560,7 +3407,7 @@
         <v>3101.983</v>
       </c>
       <c r="C22" t="n">
-        <v>3427.942833334868</v>
+        <v>16296.14303912637</v>
       </c>
       <c r="D22" t="n">
         <v>2.02506e-07</v>
@@ -3593,10 +3440,7 @@
         <v>-34801.37411946282</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.308114886164615e-11</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4028.681288404756</v>
+        <v>-12326.25276643164</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000092e-08</v>
@@ -3759,7 +3603,7 @@
         <v>4912.635</v>
       </c>
       <c r="C2" t="n">
-        <v>5249.732209477749</v>
+        <v>13246.40647605338</v>
       </c>
       <c r="D2" t="n">
         <v>1.3433e-07</v>
@@ -3792,10 +3636,7 @@
         <v>-33908.24853306253</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.773369087015149e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6198.61381657695</v>
+        <v>-7220.066343053097</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000032e-08</v>
@@ -3812,7 +3653,7 @@
         <v>4498.614</v>
       </c>
       <c r="C3" t="n">
-        <v>4804.535225420356</v>
+        <v>14068.62024221477</v>
       </c>
       <c r="D3" t="n">
         <v>1.48859e-07</v>
@@ -3845,10 +3686,7 @@
         <v>-37342.42536449764</v>
       </c>
       <c r="Y3" t="n">
-        <v>156.042014252076</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6514.737963471643</v>
+        <v>-8554.894416695637</v>
       </c>
       <c r="AA3" t="n">
         <v>1.209396741567813e-08</v>
@@ -3865,7 +3703,7 @@
         <v>4393.312</v>
       </c>
       <c r="C4" t="n">
-        <v>4694.864416878079</v>
+        <v>14128.71738174427</v>
       </c>
       <c r="D4" t="n">
         <v>1.52935e-07</v>
@@ -3898,10 +3736,7 @@
         <v>-39228.45242861607</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4680663796222e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5616.510786829333</v>
+        <v>-8740.568342406252</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000004387e-08</v>
@@ -3918,7 +3753,7 @@
         <v>4294.186</v>
       </c>
       <c r="C5" t="n">
-        <v>4615.113830600692</v>
+        <v>14603.28425728737</v>
       </c>
       <c r="D5" t="n">
         <v>1.55537e-07</v>
@@ -3951,10 +3786,7 @@
         <v>-36398.258548882</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.579283410508503e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5530.186415061746</v>
+        <v>-9302.488401432152</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000092e-08</v>
@@ -3971,7 +3803,7 @@
         <v>4235.998</v>
       </c>
       <c r="C6" t="n">
-        <v>4555.602571717726</v>
+        <v>14245.48545281569</v>
       </c>
       <c r="D6" t="n">
         <v>1.58011e-07</v>
@@ -4004,10 +3836,7 @@
         <v>-37195.25814756921</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.603317284057943e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5454.423793637969</v>
+        <v>-9010.10809393954</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000025e-08</v>
@@ -4024,7 +3853,7 @@
         <v>4203.937</v>
       </c>
       <c r="C7" t="n">
-        <v>4512.613696343234</v>
+        <v>14528.76424250767</v>
       </c>
       <c r="D7" t="n">
         <v>1.59869e-07</v>
@@ -4057,10 +3886,7 @@
         <v>-41148.04510090074</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.237446971533636e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5384.623461030998</v>
+        <v>-9356.996591763351</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000032e-08</v>
@@ -4077,7 +3903,7 @@
         <v>4128.549</v>
       </c>
       <c r="C8" t="n">
-        <v>4454.869115540784</v>
+        <v>14856.03904873458</v>
       </c>
       <c r="D8" t="n">
         <v>1.61974e-07</v>
@@ -4110,10 +3936,7 @@
         <v>-38066.11603483084</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.226689218033267e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5321.314083503124</v>
+        <v>-9751.378835359978</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000038e-08</v>
@@ -4130,7 +3953,7 @@
         <v>4100.611</v>
       </c>
       <c r="C9" t="n">
-        <v>4404.818051372833</v>
+        <v>14674.86186124616</v>
       </c>
       <c r="D9" t="n">
         <v>1.63933e-07</v>
@@ -4163,10 +3986,7 @@
         <v>-42205.13365552892</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.845792840786033e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5254.874295491088</v>
+        <v>-9624.580690561019</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000311e-08</v>
@@ -4183,7 +4003,7 @@
         <v>4037.859</v>
       </c>
       <c r="C10" t="n">
-        <v>4343.543930376985</v>
+        <v>15232.41225865398</v>
       </c>
       <c r="D10" t="n">
         <v>1.66272e-07</v>
@@ -4216,10 +4036,7 @@
         <v>-42507.3245052278</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.981389056793171e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5177.108304428417</v>
+        <v>-10261.81280608647</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000688e-08</v>
@@ -4236,7 +4053,7 @@
         <v>3944.908</v>
       </c>
       <c r="C11" t="n">
-        <v>4272.446612116149</v>
+        <v>15460.27590758329</v>
       </c>
       <c r="D11" t="n">
         <v>1.68759e-07</v>
@@ -4269,10 +4086,7 @@
         <v>-38649.88471332802</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.774713737377208e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5095.103051767225</v>
+        <v>-10566.43078891449</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4435,7 +4249,7 @@
         <v>4402.141</v>
       </c>
       <c r="C2" t="n">
-        <v>4742.911195792382</v>
+        <v>14353.51560083732</v>
       </c>
       <c r="D2" t="n">
         <v>1.52218e-07</v>
@@ -4468,10 +4282,7 @@
         <v>-39299.06508724903</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.069907534395023e-13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5593.969796945806</v>
+        <v>-8935.114471626435</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -4488,7 +4299,7 @@
         <v>4176.882000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>4488.856183852946</v>
+        <v>14242.1785188443</v>
       </c>
       <c r="D3" t="n">
         <v>1.60818e-07</v>
@@ -4521,10 +4332,7 @@
         <v>-41296.08430667601</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.221061602838329e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5346.799711738155</v>
+        <v>-9090.241437919325</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000007e-08</v>
@@ -4541,7 +4349,7 @@
         <v>4089.772</v>
       </c>
       <c r="C4" t="n">
-        <v>4401.522544350647</v>
+        <v>14666.75203201996</v>
       </c>
       <c r="D4" t="n">
         <v>1.63931e-07</v>
@@ -4574,10 +4382,7 @@
         <v>-41659.46060492302</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.61331280170005e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5248.361855837228</v>
+        <v>-9617.452277951837</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000191e-08</v>
@@ -4594,7 +4399,7 @@
         <v>4007.653</v>
       </c>
       <c r="C5" t="n">
-        <v>4338.880556047943</v>
+        <v>15137.74779735394</v>
       </c>
       <c r="D5" t="n">
         <v>1.66188e-07</v>
@@ -4627,10 +4432,7 @@
         <v>-38458.59628313041</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.237636322988008e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5179.071598703818</v>
+        <v>-10164.64466297182</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000002e-08</v>
@@ -4647,7 +4449,7 @@
         <v>3963.018</v>
       </c>
       <c r="C6" t="n">
-        <v>4292.663372178478</v>
+        <v>14641.51477003322</v>
       </c>
       <c r="D6" t="n">
         <v>1.67974e-07</v>
@@ -4680,10 +4482,7 @@
         <v>-38333.22512684517</v>
       </c>
       <c r="Y6" t="n">
-        <v>687.2649043276917</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7876.261885796946</v>
+        <v>-9710.910843460071</v>
       </c>
       <c r="AA6" t="n">
         <v>7.196377565436605e-08</v>
@@ -4700,7 +4499,7 @@
         <v>3922.402</v>
       </c>
       <c r="C7" t="n">
-        <v>4254.219198760435</v>
+        <v>15107.33244909502</v>
       </c>
       <c r="D7" t="n">
         <v>1.69672e-07</v>
@@ -4733,10 +4532,7 @@
         <v>-38832.07979608909</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.274752003741324e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5075.11129026428</v>
+        <v>-10232.67429166535</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000001e-08</v>
@@ -4753,7 +4549,7 @@
         <v>3890.286</v>
       </c>
       <c r="C8" t="n">
-        <v>4221.740789050136</v>
+        <v>14795.70491921974</v>
       </c>
       <c r="D8" t="n">
         <v>1.7081e-07</v>
@@ -4786,10 +4582,7 @@
         <v>-38781.6348465333</v>
       </c>
       <c r="Y8" t="n">
-        <v>675.6926825815557</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7672.482060935306</v>
+        <v>-9948.379317625693</v>
       </c>
       <c r="AA8" t="n">
         <v>7.042145618269329e-08</v>
@@ -4806,7 +4599,7 @@
         <v>3858.541</v>
       </c>
       <c r="C9" t="n">
-        <v>4191.652515453288</v>
+        <v>14822.23403745535</v>
       </c>
       <c r="D9" t="n">
         <v>1.72051e-07</v>
@@ -4839,10 +4632,7 @@
         <v>-38779.09752545103</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.391739878458362e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4986.619782269207</v>
+        <v>-10012.5883944097</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001939e-08</v>
@@ -4859,7 +4649,7 @@
         <v>3812.463</v>
       </c>
       <c r="C10" t="n">
-        <v>4141.695666737938</v>
+        <v>15085.17395509545</v>
       </c>
       <c r="D10" t="n">
         <v>1.73961e-07</v>
@@ -4892,10 +4682,7 @@
         <v>-39322.99022338029</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.774413729136269e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4932.622675782123</v>
+        <v>-10332.7776761962</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002892e-08</v>
@@ -4912,7 +4699,7 @@
         <v>3763.779</v>
       </c>
       <c r="C11" t="n">
-        <v>4099.776448823087</v>
+        <v>15301.16513508003</v>
       </c>
       <c r="D11" t="n">
         <v>1.75608e-07</v>
@@ -4945,10 +4732,7 @@
         <v>-39068.10437743528</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.544589170526924e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4875.627754704237</v>
+        <v>-10599.98890901813</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -4965,7 +4749,7 @@
         <v>3730.284</v>
       </c>
       <c r="C12" t="n">
-        <v>4066.272317614569</v>
+        <v>15186.05585254129</v>
       </c>
       <c r="D12" t="n">
         <v>1.77166e-07</v>
@@ -4998,10 +4782,7 @@
         <v>-39226.15035393137</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.146770044696212e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4825.287805579448</v>
+        <v>-10524.67813926793</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000032e-08</v>
@@ -5018,7 +4799,7 @@
         <v>3690.293</v>
       </c>
       <c r="C13" t="n">
-        <v>4018.225543858666</v>
+        <v>15271.46069022367</v>
       </c>
       <c r="D13" t="n">
         <v>1.79103e-07</v>
@@ -5051,10 +4832,7 @@
         <v>-39905.21080283311</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.282712548236936e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4772.860860209185</v>
+        <v>-10663.83676369994</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000006474e-08</v>
@@ -5071,7 +4849,7 @@
         <v>3645.16</v>
       </c>
       <c r="C14" t="n">
-        <v>3972.975224127933</v>
+        <v>15567.32266035649</v>
       </c>
       <c r="D14" t="n">
         <v>1.80806e-07</v>
@@ -5104,10 +4882,7 @@
         <v>-39670.48021984028</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.96436503466744e-11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4720.068396756349</v>
+        <v>-11011.57532877665</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000695e-08</v>
@@ -5124,7 +4899,7 @@
         <v>3601.341</v>
       </c>
       <c r="C15" t="n">
-        <v>3940.189726342663</v>
+        <v>15399.66978230092</v>
       </c>
       <c r="D15" t="n">
         <v>1.82497e-07</v>
@@ -5157,10 +4932,7 @@
         <v>-39362.1724007397</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.223557271580338e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4668.477725603038</v>
+        <v>-10886.71337700048</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000003895e-08</v>
@@ -5177,7 +4949,7 @@
         <v>3569.599</v>
       </c>
       <c r="C16" t="n">
-        <v>3900.62186051976</v>
+        <v>15281.01462736756</v>
       </c>
       <c r="D16" t="n">
         <v>1.84262e-07</v>
@@ -5210,10 +4982,7 @@
         <v>-40108.51101148343</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.794250209153397e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4618.882575235939</v>
+        <v>-10810.57532899204</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000005248e-08</v>
@@ -5230,7 +4999,7 @@
         <v>3526.349</v>
       </c>
       <c r="C17" t="n">
-        <v>3858.346951867173</v>
+        <v>15280.20979793295</v>
       </c>
       <c r="D17" t="n">
         <v>1.86058e-07</v>
@@ -5263,10 +5032,7 @@
         <v>-40216.60342380321</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.190897162003965e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4566.912528205035</v>
+        <v>-10857.18264397096</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000057676e-08</v>
@@ -5283,7 +5049,7 @@
         <v>3485.29</v>
       </c>
       <c r="C18" t="n">
-        <v>3814.785485002801</v>
+        <v>15490.23795446496</v>
       </c>
       <c r="D18" t="n">
         <v>1.87802e-07</v>
@@ -5316,10 +5082,7 @@
         <v>-39780.26452467556</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.50755715247912e-15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4513.390920273878</v>
+        <v>-11117.08397236712</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -5336,7 +5099,7 @@
         <v>3424.659</v>
       </c>
       <c r="C19" t="n">
-        <v>3770.693187163068</v>
+        <v>15919.32291303107</v>
       </c>
       <c r="D19" t="n">
         <v>1.89428e-07</v>
@@ -5369,10 +5132,7 @@
         <v>-36818.62030796455</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.652601395390524e-13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4466.6218191977</v>
+        <v>-11597.96569228346</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000005e-08</v>
@@ -5389,7 +5149,7 @@
         <v>3407.722</v>
       </c>
       <c r="C20" t="n">
-        <v>3740.818133126701</v>
+        <v>15800.14225479331</v>
       </c>
       <c r="D20" t="n">
         <v>1.91044e-07</v>
@@ -5422,10 +5182,7 @@
         <v>-40027.94159072722</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.337863568645199e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4417.126726544804</v>
+        <v>-11517.67089349847</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000031e-08</v>
@@ -5442,7 +5199,7 @@
         <v>3350.828</v>
       </c>
       <c r="C21" t="n">
-        <v>3696.006652664463</v>
+        <v>16019.96027689577</v>
       </c>
       <c r="D21" t="n">
         <v>1.92914e-07</v>
@@ -5475,10 +5232,7 @@
         <v>-36600.3077126623</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.279026472579868e-11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4369.706001322709</v>
+        <v>-11787.10696800769</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000139e-08</v>
@@ -5495,7 +5249,7 @@
         <v>3324.337</v>
       </c>
       <c r="C22" t="n">
-        <v>3658.638213383156</v>
+        <v>15943.51790224986</v>
       </c>
       <c r="D22" t="n">
         <v>1.94327e-07</v>
@@ -5528,10 +5282,7 @@
         <v>-37075.51164119769</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.252783642140035e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4327.200546711805</v>
+        <v>-11745.06348280174</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000022e-08</v>
@@ -5694,7 +5445,7 @@
         <v>5171.343</v>
       </c>
       <c r="C2" t="n">
-        <v>5574.912123415053</v>
+        <v>13298.03193107421</v>
       </c>
       <c r="D2" t="n">
         <v>1.25118e-07</v>
@@ -5727,10 +5478,7 @@
         <v>-31288.80431221858</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.3727882650652</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7531.255893526579</v>
+        <v>-6897.323596005216</v>
       </c>
       <c r="AA2" t="n">
         <v>1.423198283725921e-08</v>
@@ -5747,7 +5495,7 @@
         <v>4432.228</v>
       </c>
       <c r="C3" t="n">
-        <v>4763.316159328083</v>
+        <v>14086.31888839032</v>
       </c>
       <c r="D3" t="n">
         <v>1.48536e-07</v>
@@ -5780,10 +5528,7 @@
         <v>-34444.15099765697</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.753490218562992e-14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5662.921373613473</v>
+        <v>-8582.312242540902</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -5800,7 +5545,7 @@
         <v>4246.938</v>
       </c>
       <c r="C4" t="n">
-        <v>4574.815254730323</v>
+        <v>14269.68548494435</v>
       </c>
       <c r="D4" t="n">
         <v>1.55454e-07</v>
@@ -5833,10 +5578,7 @@
         <v>-35796.28476033612</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.077429156655222e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5453.727257515189</v>
+        <v>-8986.354570919395</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000002162e-08</v>
@@ -5853,7 +5595,7 @@
         <v>4145.025000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>4482.166217714448</v>
+        <v>14298.27348991597</v>
       </c>
       <c r="D5" t="n">
         <v>1.58499e-07</v>
@@ -5886,10 +5628,7 @@
         <v>-34021.32470235737</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.005883091006426e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5362.1644611844</v>
+        <v>-9104.595029824779</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000007036e-08</v>
@@ -5906,7 +5645,7 @@
         <v>4097.360000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>4422.820774889178</v>
+        <v>14437.11999369038</v>
       </c>
       <c r="D6" t="n">
         <v>1.61178e-07</v>
@@ -5939,10 +5678,7 @@
         <v>-37351.45396210863</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.237157387013213e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5276.59588906396</v>
+        <v>-9325.613406851939</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000004e-08</v>
@@ -5959,7 +5695,7 @@
         <v>4014.645</v>
       </c>
       <c r="C7" t="n">
-        <v>4356.337983501533</v>
+        <v>15218.11954303348</v>
       </c>
       <c r="D7" t="n">
         <v>1.63544e-07</v>
@@ -5992,10 +5728,7 @@
         <v>-35221.65591419528</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.604080970376257e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5206.980093308081</v>
+        <v>-10190.65647586754</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000031e-08</v>
@@ -6012,7 +5745,7 @@
         <v>3958.379</v>
       </c>
       <c r="C8" t="n">
-        <v>4303.411901900567</v>
+        <v>15211.20038535372</v>
       </c>
       <c r="D8" t="n">
         <v>1.65559e-07</v>
@@ -6045,10 +5778,7 @@
         <v>-35418.58196609704</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.084588044883743e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5136.521880209947</v>
+        <v>-10243.08512027153</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000003492e-08</v>
@@ -6065,7 +5795,7 @@
         <v>3895.914</v>
       </c>
       <c r="C9" t="n">
-        <v>4247.567658844417</v>
+        <v>15288.67574978406</v>
       </c>
       <c r="D9" t="n">
         <v>1.677e-07</v>
@@ -6098,10 +5828,7 @@
         <v>-35334.28222786605</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.606270498379967e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5066.026369261791</v>
+        <v>-10384.41606270575</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000447e-08</v>
@@ -6118,7 +5845,7 @@
         <v>3844.036</v>
       </c>
       <c r="C10" t="n">
-        <v>4190.498029460265</v>
+        <v>15604.96231673095</v>
       </c>
       <c r="D10" t="n">
         <v>1.69951e-07</v>
@@ -6151,10 +5878,7 @@
         <v>-36014.23976485474</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.196625497896767e-12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4997.020269697509</v>
+        <v>-10770.00728757267</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000068e-08</v>
@@ -6171,7 +5895,7 @@
         <v>3793.37</v>
       </c>
       <c r="C11" t="n">
-        <v>4141.190741514576</v>
+        <v>15315.96105193299</v>
       </c>
       <c r="D11" t="n">
         <v>1.72019e-07</v>
@@ -6204,10 +5928,7 @@
         <v>-36521.77680701915</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.323720389410133e-16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4934.457911713206</v>
+        <v>-10533.76681014214</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6370,7 +6091,7 @@
         <v>4136.258000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>4482.487995456688</v>
+        <v>13713.6726669812</v>
       </c>
       <c r="D2" t="n">
         <v>1.59485e-07</v>
@@ -6403,10 +6124,7 @@
         <v>-33825.26184319972</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.055618607895975e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5290.061734678266</v>
+        <v>-8524.61462723669</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000019e-08</v>
@@ -6423,7 +6141,7 @@
         <v>3952.457</v>
       </c>
       <c r="C3" t="n">
-        <v>4281.049828663809</v>
+        <v>14227.34794756743</v>
       </c>
       <c r="D3" t="n">
         <v>1.6696e-07</v>
@@ -6456,10 +6174,7 @@
         <v>-35330.39005253768</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.705137972537033e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5085.916792003528</v>
+        <v>-9271.739248273789</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000114e-08</v>
@@ -6476,7 +6191,7 @@
         <v>3882.862</v>
       </c>
       <c r="C4" t="n">
-        <v>4206.779652213148</v>
+        <v>14008.55816361448</v>
       </c>
       <c r="D4" t="n">
         <v>1.68079e-07</v>
@@ -6509,10 +6224,7 @@
         <v>-31714.00810052</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.438550148681307e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5010.869416476461</v>
+        <v>-9116.155589038912</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000049e-08</v>
@@ -6529,7 +6241,7 @@
         <v>3833.271999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>4164.182615171735</v>
+        <v>14566.96043859751</v>
       </c>
       <c r="D5" t="n">
         <v>1.70118e-07</v>
@@ -6562,10 +6274,7 @@
         <v>-33265.9530777757</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.6482019792596</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5750.296419847661</v>
+        <v>-9729.861697848577</v>
       </c>
       <c r="AA5" t="n">
         <v>1.508954410429453e-08</v>
@@ -6582,7 +6291,7 @@
         <v>3787.416999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>4119.023947544148</v>
+        <v>14933.37565288251</v>
       </c>
       <c r="D6" t="n">
         <v>1.71893e-07</v>
@@ -6615,10 +6324,7 @@
         <v>-33949.97400845637</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.72424720933545e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4893.829684938073</v>
+        <v>-10149.74203073628</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000012e-08</v>
@@ -6635,7 +6341,7 @@
         <v>3747.302</v>
       </c>
       <c r="C7" t="n">
-        <v>4073.799750050469</v>
+        <v>14822.78820500917</v>
       </c>
       <c r="D7" t="n">
         <v>1.73724e-07</v>
@@ -6668,10 +6374,7 @@
         <v>-34750.43855912846</v>
       </c>
       <c r="Y7" t="n">
-        <v>649.425138428979</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7372.658546923845</v>
+        <v>-10087.07427714352</v>
       </c>
       <c r="AA7" t="n">
         <v>7.475419789424068e-08</v>
@@ -6688,7 +6391,7 @@
         <v>3699.331</v>
       </c>
       <c r="C8" t="n">
-        <v>4030.908855449173</v>
+        <v>15275.96128364949</v>
       </c>
       <c r="D8" t="n">
         <v>1.75619e-07</v>
@@ -6721,10 +6424,7 @@
         <v>-34773.63029695822</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.370902254011373e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4781.129777845021</v>
+        <v>-10599.65779120864</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000141e-08</v>
@@ -6741,7 +6441,7 @@
         <v>3657.599</v>
       </c>
       <c r="C9" t="n">
-        <v>3988.035422692396</v>
+        <v>15287.08041767981</v>
       </c>
       <c r="D9" t="n">
         <v>1.7739e-07</v>
@@ -6774,10 +6474,7 @@
         <v>-35449.25092062458</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.116457575384542e-15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4729.892920735024</v>
+        <v>-10659.05778477437</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6794,7 +6491,7 @@
         <v>3622.848</v>
       </c>
       <c r="C10" t="n">
-        <v>3954.551676450738</v>
+        <v>15480.1619182235</v>
       </c>
       <c r="D10" t="n">
         <v>1.78938e-07</v>
@@ -6827,10 +6524,7 @@
         <v>-35666.33351180466</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35953818672846e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4682.741197291212</v>
+        <v>-10897.8761180063</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000014e-08</v>
@@ -6847,7 +6541,7 @@
         <v>3583.788</v>
       </c>
       <c r="C11" t="n">
-        <v>3915.24934647971</v>
+        <v>15204.65988274714</v>
       </c>
       <c r="D11" t="n">
         <v>1.80722e-07</v>
@@ -6880,10 +6574,7 @@
         <v>-35831.69351399129</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.326588828358574e-13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4634.452873220527</v>
+        <v>-10664.02643746488</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6900,7 +6591,7 @@
         <v>3543.513</v>
       </c>
       <c r="C12" t="n">
-        <v>3876.053059089986</v>
+        <v>15512.27738113279</v>
       </c>
       <c r="D12" t="n">
         <v>1.8242e-07</v>
@@ -6933,10 +6624,7 @@
         <v>-36136.98844806143</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.293114410044997e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4586.643044613477</v>
+        <v>-11022.42902598979</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000034e-08</v>
@@ -6953,7 +6641,7 @@
         <v>3487.706</v>
       </c>
       <c r="C13" t="n">
-        <v>3831.430229637688</v>
+        <v>15837.72857135308</v>
       </c>
       <c r="D13" t="n">
         <v>1.8382e-07</v>
@@ -6986,10 +6674,7 @@
         <v>-33245.81916992066</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.018720049496159e-13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4541.795260246833</v>
+        <v>-11392.12585593503</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -7006,7 +6691,7 @@
         <v>3474.855</v>
       </c>
       <c r="C14" t="n">
-        <v>3807.830676038274</v>
+        <v>15595.5808260762</v>
       </c>
       <c r="D14" t="n">
         <v>1.8567e-07</v>
@@ -7039,10 +6724,7 @@
         <v>-36799.36063552356</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.540312836456596e-11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4496.128594752121</v>
+        <v>-11191.2230521835</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000002e-08</v>
@@ -7059,7 +6741,7 @@
         <v>3443.096</v>
       </c>
       <c r="C15" t="n">
-        <v>3769.417598548494</v>
+        <v>15925.41249048567</v>
       </c>
       <c r="D15" t="n">
         <v>1.87101e-07</v>
@@ -7092,10 +6774,7 @@
         <v>-37066.46577169808</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.36046322035644e-11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4452.563090708637</v>
+        <v>-11565.57297711398</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000002e-08</v>
@@ -7112,7 +6791,7 @@
         <v>3404.245</v>
       </c>
       <c r="C16" t="n">
-        <v>3731.700633865903</v>
+        <v>16023.56724656247</v>
       </c>
       <c r="D16" t="n">
         <v>1.88897e-07</v>
@@ -7145,10 +6824,7 @@
         <v>-36823.19557087034</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.021803329851366e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4405.087504053349</v>
+        <v>-11710.09788761022</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000002e-08</v>
@@ -7165,7 +6841,7 @@
         <v>3373.864</v>
       </c>
       <c r="C17" t="n">
-        <v>3700.679683437095</v>
+        <v>15642.08052183993</v>
       </c>
       <c r="D17" t="n">
         <v>1.90441e-07</v>
@@ -7198,10 +6874,7 @@
         <v>-37281.29921870473</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.937037436539442e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4361.65046224517</v>
+        <v>-11361.1849903189</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000063e-08</v>
@@ -7218,7 +6891,7 @@
         <v>3334.496</v>
       </c>
       <c r="C18" t="n">
-        <v>3663.987226290485</v>
+        <v>15793.86092614864</v>
       </c>
       <c r="D18" t="n">
         <v>1.92083e-07</v>
@@ -7251,10 +6924,7 @@
         <v>-37364.84726580631</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.117002960450743e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4315.182614029754</v>
+        <v>-11557.83495941481</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000085e-08</v>
@@ -7271,7 +6941,7 @@
         <v>3301.107</v>
       </c>
       <c r="C19" t="n">
-        <v>3627.848680302762</v>
+        <v>15587.40865188516</v>
       </c>
       <c r="D19" t="n">
         <v>1.93752e-07</v>
@@ -7304,10 +6974,7 @@
         <v>-37950.20597697044</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.126596720750614e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4266.882086286062</v>
+        <v>-11390.36122054744</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000008e-08</v>
@@ -7324,7 +6991,7 @@
         <v>3242.685</v>
       </c>
       <c r="C20" t="n">
-        <v>3581.978223539385</v>
+        <v>16193.75473120412</v>
       </c>
       <c r="D20" t="n">
         <v>1.95656e-07</v>
@@ -7357,10 +7024,7 @@
         <v>-34332.36346698591</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.679406849722052e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4220.201840364709</v>
+        <v>-12053.59460236687</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000053e-08</v>
@@ -7377,7 +7041,7 @@
         <v>3205.215</v>
       </c>
       <c r="C21" t="n">
-        <v>3540.94067960953</v>
+        <v>16214.9749873977</v>
       </c>
       <c r="D21" t="n">
         <v>1.97413e-07</v>
@@ -7410,10 +7074,7 @@
         <v>-34458.29171334921</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.817174536290988e-13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4171.953804259084</v>
+        <v>-12118.91098389381</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7430,7 +7091,7 @@
         <v>3186.589</v>
       </c>
       <c r="C22" t="n">
-        <v>3510.831799213346</v>
+        <v>15842.93073027041</v>
       </c>
       <c r="D22" t="n">
         <v>1.99301e-07</v>
@@ -7463,10 +7124,7 @@
         <v>-37994.63339622974</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.568152257954956e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4121.861361445171</v>
+        <v>-11786.19714660002</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000077e-08</v>
@@ -7629,7 +7287,7 @@
         <v>4348.036</v>
       </c>
       <c r="C2" t="n">
-        <v>4700.280106175786</v>
+        <v>14124.23771154732</v>
       </c>
       <c r="D2" t="n">
         <v>1.51106e-07</v>
@@ -7662,10 +7320,7 @@
         <v>-33687.62592358021</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.942065437854256e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5477.383319260361</v>
+        <v>-8695.935790847527</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -7682,7 +7337,7 @@
         <v>3940.101000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>4272.403213518042</v>
+        <v>14694.44609965154</v>
       </c>
       <c r="D3" t="n">
         <v>1.66723e-07</v>
@@ -7715,10 +7370,7 @@
         <v>-35133.67311096831</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.031921924648365e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5070.109834270832</v>
+        <v>-9747.884926903269</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001138e-08</v>
@@ -7735,7 +7387,7 @@
         <v>3843.614</v>
       </c>
       <c r="C4" t="n">
-        <v>4170.434219421229</v>
+        <v>15084.06057031807</v>
       </c>
       <c r="D4" t="n">
         <v>1.71e-07</v>
@@ -7768,10 +7420,7 @@
         <v>-36478.51756397505</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.302392021020318e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4958.757284769948</v>
+        <v>-10265.029935544</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000359e-08</v>
@@ -7788,7 +7437,7 @@
         <v>3780.592</v>
       </c>
       <c r="C5" t="n">
-        <v>4112.35277809266</v>
+        <v>15196.51827572117</v>
       </c>
       <c r="D5" t="n">
         <v>1.73286e-07</v>
@@ -7821,10 +7470,7 @@
         <v>-36588.03756259455</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.760648399349517e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4885.252140003793</v>
+        <v>-10445.34132482669</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000004e-08</v>
@@ -7841,7 +7487,7 @@
         <v>3728.027</v>
       </c>
       <c r="C6" t="n">
-        <v>4057.232453020977</v>
+        <v>15632.0500986056</v>
       </c>
       <c r="D6" t="n">
         <v>1.75587e-07</v>
@@ -7874,10 +7520,7 @@
         <v>-37245.3670325428</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.347109086816492e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4817.172109067823</v>
+        <v>-10952.90289628668</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000029e-08</v>
@@ -7894,7 +7537,7 @@
         <v>3675.832</v>
       </c>
       <c r="C7" t="n">
-        <v>4004.464255156422</v>
+        <v>15014.90839392742</v>
       </c>
       <c r="D7" t="n">
         <v>1.77914e-07</v>
@@ -7927,10 +7570,7 @@
         <v>-37423.539315622</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.922653631191028e-14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4749.530399016374</v>
+        <v>-10386.94471769261</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000084e-08</v>
@@ -7947,7 +7587,7 @@
         <v>3616.231</v>
       </c>
       <c r="C8" t="n">
-        <v>3948.310602164721</v>
+        <v>15474.87777736861</v>
       </c>
       <c r="D8" t="n">
         <v>1.80104e-07</v>
@@ -7980,10 +7620,7 @@
         <v>-37456.40819670396</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.066068112178194e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4679.990620401043</v>
+        <v>-10917.11670020701</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8000,7 +7637,7 @@
         <v>3558.578</v>
       </c>
       <c r="C9" t="n">
-        <v>3893.523923085867</v>
+        <v>15788.52041369195</v>
       </c>
       <c r="D9" t="n">
         <v>1.82413e-07</v>
@@ -8033,10 +7670,7 @@
         <v>-37692.05755682214</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.491441902219318e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4613.543397317023</v>
+        <v>-11298.20678894136</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8053,7 +7687,7 @@
         <v>3509.456</v>
       </c>
       <c r="C10" t="n">
-        <v>3842.582873168538</v>
+        <v>15786.1233324903</v>
       </c>
       <c r="D10" t="n">
         <v>1.84824e-07</v>
@@ -8086,10 +7720,7 @@
         <v>-38196.74860145761</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.149180429125523e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4547.565266176706</v>
+        <v>-11358.20291697597</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000723e-08</v>
@@ -8106,7 +7737,7 @@
         <v>3436.622</v>
       </c>
       <c r="C11" t="n">
-        <v>3786.307367924245</v>
+        <v>15834.35869849383</v>
       </c>
       <c r="D11" t="n">
         <v>1.87218e-07</v>
@@ -8139,10 +7770,7 @@
         <v>-34924.61575157676</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.757646146159926e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4482.094117434618</v>
+        <v>-11468.42476240935</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000152e-08</v>
@@ -8305,7 +7933,7 @@
         <v>4125.245</v>
       </c>
       <c r="C2" t="n">
-        <v>4483.163801408125</v>
+        <v>14699.47286336804</v>
       </c>
       <c r="D2" t="n">
         <v>1.60268e-07</v>
@@ -8338,10 +7966,7 @@
         <v>-35459.49918933259</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.578942527089263e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5279.715469654875</v>
+        <v>-9551.876061931474</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000011e-08</v>
@@ -8358,7 +7983,7 @@
         <v>3945.581000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>4259.132188697948</v>
+        <v>15153.01746974672</v>
       </c>
       <c r="D3" t="n">
         <v>1.68472e-07</v>
@@ -8391,10 +8016,7 @@
         <v>-40804.69454185351</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.415940276857433e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5056.057124311519</v>
+        <v>-10259.0071394878</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000009e-08</v>
@@ -8411,7 +8033,7 @@
         <v>3854.231</v>
       </c>
       <c r="C4" t="n">
-        <v>4183.069836279103</v>
+        <v>15190.40774311236</v>
       </c>
       <c r="D4" t="n">
         <v>1.7086e-07</v>
@@ -8444,10 +8066,7 @@
         <v>-37058.26039217741</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.130217462671344e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4977.812928261335</v>
+        <v>-10367.91720366388</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000009e-08</v>
@@ -8464,7 +8083,7 @@
         <v>3798.029</v>
       </c>
       <c r="C5" t="n">
-        <v>4128.305020271271</v>
+        <v>15546.46620885118</v>
       </c>
       <c r="D5" t="n">
         <v>1.72934e-07</v>
@@ -8497,10 +8116,7 @@
         <v>-37157.89408818304</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.926527047309575e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4912.408834477734</v>
+        <v>-10790.61643477461</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000487e-08</v>
@@ -8517,7 +8133,7 @@
         <v>3745.503</v>
       </c>
       <c r="C6" t="n">
-        <v>4081.255735069864</v>
+        <v>15450.39664022522</v>
       </c>
       <c r="D6" t="n">
         <v>1.75009e-07</v>
@@ -8550,10 +8166,7 @@
         <v>-37200.92078219755</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.378547265192882e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4848.606570220082</v>
+        <v>-10751.21743604235</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001022e-08</v>
@@ -8570,7 +8183,7 @@
         <v>3701.435</v>
       </c>
       <c r="C7" t="n">
-        <v>4034.318880028927</v>
+        <v>14942.01483377119</v>
       </c>
       <c r="D7" t="n">
         <v>1.76893e-07</v>
@@ -8603,10 +8216,7 @@
         <v>-37106.55806431301</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.755685527576211e-18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4790.674496682132</v>
+        <v>-10283.08967242077</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -8623,7 +8233,7 @@
         <v>3654.411</v>
       </c>
       <c r="C8" t="n">
-        <v>3986.167668749661</v>
+        <v>15670.03027054642</v>
       </c>
       <c r="D8" t="n">
         <v>1.78711e-07</v>
@@ -8656,10 +8266,7 @@
         <v>-37421.76169513446</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.561718769437166e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4732.368596217309</v>
+        <v>-11076.69928999937</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000002686e-08</v>
@@ -8676,7 +8283,7 @@
         <v>3604.128</v>
       </c>
       <c r="C9" t="n">
-        <v>3938.47345351722</v>
+        <v>15777.56280457579</v>
       </c>
       <c r="D9" t="n">
         <v>1.81076e-07</v>
@@ -8709,10 +8316,7 @@
         <v>-37628.80472119674</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.860075500833695e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4667.655583209818</v>
+        <v>-11247.29597249553</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000022e-08</v>
@@ -8729,7 +8333,7 @@
         <v>3557.757</v>
       </c>
       <c r="C10" t="n">
-        <v>3888.941179975794</v>
+        <v>15591.65566763965</v>
       </c>
       <c r="D10" t="n">
         <v>1.83017e-07</v>
@@ -8762,10 +8366,7 @@
         <v>-37753.35710722775</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.346757406467763e-13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4607.999201860185</v>
+        <v>-11110.06221658947</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8782,7 +8383,7 @@
         <v>3514.675</v>
       </c>
       <c r="C11" t="n">
-        <v>3847.390231754518</v>
+        <v>15395.85767686268</v>
       </c>
       <c r="D11" t="n">
         <v>1.85024e-07</v>
@@ -8815,10 +8416,7 @@
         <v>-38003.53013943938</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.234129074521629e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4555.82157803937</v>
+        <v>-10962.24444473221</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000521e-08</v>
@@ -8835,7 +8433,7 @@
         <v>3459.314</v>
       </c>
       <c r="C12" t="n">
-        <v>3802.548247462247</v>
+        <v>15631.13283480043</v>
       </c>
       <c r="D12" t="n">
         <v>1.86781e-07</v>
@@ -8868,10 +8466,7 @@
         <v>-35480.36594929602</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.352918440935144e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4504.749585845556</v>
+        <v>-11247.40602477104</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000001008e-08</v>
@@ -8888,7 +8483,7 @@
         <v>3436.244</v>
       </c>
       <c r="C13" t="n">
-        <v>3762.847249333924</v>
+        <v>15539.49568476772</v>
       </c>
       <c r="D13" t="n">
         <v>1.88562e-07</v>
@@ -8921,10 +8516,7 @@
         <v>-38441.92758441687</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.699898045402136e-11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4455.872518916538</v>
+        <v>-11199.8567150622</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000155e-08</v>
@@ -8941,7 +8533,7 @@
         <v>3399.643</v>
       </c>
       <c r="C14" t="n">
-        <v>3731.557428663083</v>
+        <v>15450.21329110568</v>
       </c>
       <c r="D14" t="n">
         <v>1.90275e-07</v>
@@ -8974,10 +8566,7 @@
         <v>-38484.186870261</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.353173624462726e-12</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4407.312585899738</v>
+        <v>-11152.26013846273</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000163e-08</v>
@@ -8994,7 +8583,7 @@
         <v>3363.146</v>
       </c>
       <c r="C15" t="n">
-        <v>3692.590646104326</v>
+        <v>15541.88425628435</v>
       </c>
       <c r="D15" t="n">
         <v>1.9224e-07</v>
@@ -9027,10 +8616,7 @@
         <v>-38904.05113185586</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.89790878882165e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4358.651490445566</v>
+        <v>-11291.8880914134</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000002352e-08</v>
@@ -9047,7 +8633,7 @@
         <v>3323.491</v>
       </c>
       <c r="C16" t="n">
-        <v>3656.200500423397</v>
+        <v>15407.00582820039</v>
       </c>
       <c r="D16" t="n">
         <v>1.93855e-07</v>
@@ -9080,10 +8666,7 @@
         <v>-38576.84392692149</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.05632159524709e-13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4308.860573263448</v>
+        <v>-11196.31070877813</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000005e-08</v>
@@ -9100,7 +8683,7 @@
         <v>3280.727</v>
       </c>
       <c r="C17" t="n">
-        <v>3611.300891899984</v>
+        <v>16049.15958170829</v>
       </c>
       <c r="D17" t="n">
         <v>1.95844e-07</v>
@@ -9133,10 +8716,7 @@
         <v>-39053.92654966771</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.630101072426787e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4258.310975849784</v>
+        <v>-11898.65993287348</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000098e-08</v>
@@ -9153,7 +8733,7 @@
         <v>3230.648</v>
       </c>
       <c r="C18" t="n">
-        <v>3568.325696749039</v>
+        <v>15497.48098836415</v>
       </c>
       <c r="D18" t="n">
         <v>1.975e-07</v>
@@ -9186,10 +8766,7 @@
         <v>-35406.24683018366</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.653147173285814e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4215.906234041012</v>
+        <v>-11376.42428639864</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000035e-08</v>
@@ -9206,7 +8783,7 @@
         <v>3191.834</v>
       </c>
       <c r="C19" t="n">
-        <v>3530.528851892328</v>
+        <v>15846.37710487785</v>
       </c>
       <c r="D19" t="n">
         <v>1.99353e-07</v>
@@ -9239,10 +8816,7 @@
         <v>-35335.5783293213</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.741472560869826e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4165.342381465651</v>
+        <v>-11776.14107971936</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000038e-08</v>
@@ -9259,7 +8833,7 @@
         <v>3153.2</v>
       </c>
       <c r="C20" t="n">
-        <v>3491.668940095174</v>
+        <v>15814.66808159137</v>
       </c>
       <c r="D20" t="n">
         <v>2.01235e-07</v>
@@ -9292,10 +8866,7 @@
         <v>-35730.55346404164</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.933566329209869e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4116.21004738066</v>
+        <v>-11788.4796410267</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000058e-08</v>
@@ -9312,7 +8883,7 @@
         <v>3116.067</v>
       </c>
       <c r="C21" t="n">
-        <v>3456.225967248421</v>
+        <v>16186.30939155372</v>
       </c>
       <c r="D21" t="n">
         <v>2.03047e-07</v>
@@ -9345,10 +8916,7 @@
         <v>-35747.03203606453</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.496179118674745e-10</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4068.479807315798</v>
+        <v>-12210.09969469975</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000158e-08</v>
@@ -9365,7 +8933,7 @@
         <v>3083.189</v>
       </c>
       <c r="C22" t="n">
-        <v>3418.46550043226</v>
+        <v>15923.75046616629</v>
       </c>
       <c r="D22" t="n">
         <v>2.04658e-07</v>
@@ -9398,10 +8966,7 @@
         <v>-35584.73239452662</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.071552598642541e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4024.86388408256</v>
+        <v>-11981.68494157679</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000174e-08</v>
@@ -9564,7 +9129,7 @@
         <v>2712.444</v>
       </c>
       <c r="C2" t="n">
-        <v>3090.249317850884</v>
+        <v>18220.33511395426</v>
       </c>
       <c r="D2" t="n">
         <v>2.16796e-07</v>
@@ -9597,10 +9162,7 @@
         <v>-32236.99561332318</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.272466868428998e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3619.454970916422</v>
+        <v>-14623.84809458124</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000035e-08</v>
@@ -9617,7 +9179,7 @@
         <v>2677.859</v>
       </c>
       <c r="C3" t="n">
-        <v>3075.190504058026</v>
+        <v>17815.46773053482</v>
       </c>
       <c r="D3" t="n">
         <v>2.18813e-07</v>
@@ -9650,10 +9212,7 @@
         <v>-31024.58802592076</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.59725507536361e-13</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3592.977572070574</v>
+        <v>-14249.14200118081</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000019e-08</v>
@@ -9670,7 +9229,7 @@
         <v>2644.616</v>
       </c>
       <c r="C4" t="n">
-        <v>3035.331626809811</v>
+        <v>18002.52050016884</v>
       </c>
       <c r="D4" t="n">
         <v>2.21057e-07</v>
@@ -9703,10 +9262,7 @@
         <v>-31406.85924389338</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.798435387751001e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3549.577884851644</v>
+        <v>-14483.14829710198</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000018e-08</v>
@@ -9723,7 +9279,7 @@
         <v>2589.299</v>
       </c>
       <c r="C5" t="n">
-        <v>2989.662409218816</v>
+        <v>18374.94736697934</v>
       </c>
       <c r="D5" t="n">
         <v>2.2363e-07</v>
@@ -9756,10 +9312,7 @@
         <v>-31402.3265957985</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.708585652094037e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3476.110299697852</v>
+        <v>-14918.76498180039</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002916e-08</v>
@@ -9776,7 +9329,7 @@
         <v>2510.877</v>
       </c>
       <c r="C6" t="n">
-        <v>2911.944225855837</v>
+        <v>18745.55527608566</v>
       </c>
       <c r="D6" t="n">
         <v>2.27372e-07</v>
@@ -9809,10 +9362,7 @@
         <v>-29914.60610940552</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.373108012083583e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3397.295857059149</v>
+        <v>-15373.88627647562</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000018e-08</v>
@@ -9829,7 +9379,7 @@
         <v>2447.341</v>
       </c>
       <c r="C7" t="n">
-        <v>2856.221631062224</v>
+        <v>18669.32123158079</v>
       </c>
       <c r="D7" t="n">
         <v>2.30685e-07</v>
@@ -9862,10 +9412,7 @@
         <v>-29911.33831462153</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.554197580282301e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3316.466220036885</v>
+        <v>-15367.39622986894</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000005e-08</v>
@@ -9882,7 +9429,7 @@
         <v>2386.682</v>
       </c>
       <c r="C8" t="n">
-        <v>2796.704582437426</v>
+        <v>19278.51120631321</v>
       </c>
       <c r="D8" t="n">
         <v>2.34173e-07</v>
@@ -9915,10 +9462,7 @@
         <v>-31741.5903753325</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.110356629220958e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3230.539140002104</v>
+        <v>-16058.25759881334</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000015e-08</v>
@@ -9935,7 +9479,7 @@
         <v>2304.896</v>
       </c>
       <c r="C9" t="n">
-        <v>2724.179088907667</v>
+        <v>19475.29638872886</v>
       </c>
       <c r="D9" t="n">
         <v>2.38033e-07</v>
@@ -9968,10 +9512,7 @@
         <v>-29779.75380431334</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.473947042753324e-14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3144.604814122403</v>
+        <v>-16338.65749020458</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9988,7 +9529,7 @@
         <v>2244.728</v>
       </c>
       <c r="C10" t="n">
-        <v>2657.804984220966</v>
+        <v>19611.59482151355</v>
       </c>
       <c r="D10" t="n">
         <v>2.41739e-07</v>
@@ -10021,10 +9562,7 @@
         <v>-29821.95377418316</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.364170239848895e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3064.205932408323</v>
+        <v>-16551.40978768719</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000038e-08</v>
@@ -10041,7 +9579,7 @@
         <v>2171.918</v>
       </c>
       <c r="C11" t="n">
-        <v>2588.76261300549</v>
+        <v>20169.88930497447</v>
       </c>
       <c r="D11" t="n">
         <v>2.44954e-07</v>
@@ -10074,10 +9612,7 @@
         <v>-27664.32041898106</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.400856975976487e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2985.807381026741</v>
+        <v>-17183.63227361515</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000002247e-08</v>
